--- a/bakımrecete.xlsx
+++ b/bakımrecete.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="BuÇalışmaKitabı"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="-30" windowWidth="9150" windowHeight="7560" tabRatio="756" activeTab="1"/>
+    <workbookView xWindow="15" yWindow="-30" windowWidth="9150" windowHeight="7560" tabRatio="756" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="bakimrecete" sheetId="6" r:id="rId1"/>
@@ -1763,6 +1763,9 @@
     <xf numFmtId="1" fontId="7" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1771,9 +1774,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2136,11 +2136,11 @@
       </c>
       <c r="G2" s="48">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H2" s="48">
         <f>E2*G2</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2192,11 +2192,11 @@
       </c>
       <c r="G4" s="48">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
       <c r="H4" s="48">
         <f t="shared" si="0"/>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
     </row>
     <row r="5" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="H8" s="48">
         <f>SUBTOTAL(9,H2:H7)</f>
-        <v>188.33581395348835</v>
+        <v>196.87020195348836</v>
       </c>
     </row>
     <row r="9" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2322,11 +2322,11 @@
       </c>
       <c r="G9" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H9" s="49">
         <f t="shared" si="0"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2378,11 +2378,11 @@
       </c>
       <c r="G11" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
       <c r="H11" s="49">
         <f t="shared" si="0"/>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="H15" s="49">
         <f>SUBTOTAL(9,H9:H14)</f>
-        <v>188.33581395348835</v>
+        <v>196.87020195348836</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2508,11 +2508,11 @@
       </c>
       <c r="G16" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H16" s="49">
         <f t="shared" si="0"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2564,11 +2564,11 @@
       </c>
       <c r="G18" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H18" s="49">
         <f t="shared" si="0"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2592,11 +2592,11 @@
       </c>
       <c r="G19" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.83</v>
+        <v>21.283352999999998</v>
       </c>
       <c r="H19" s="49">
         <f t="shared" si="0"/>
-        <v>11.83</v>
+        <v>21.283352999999998</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2620,11 +2620,11 @@
       </c>
       <c r="G20" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>16.309999999999999</v>
+        <v>29.343320999999996</v>
       </c>
       <c r="H20" s="49">
         <f t="shared" si="0"/>
-        <v>16.309999999999999</v>
+        <v>29.343320999999996</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2648,11 +2648,11 @@
       </c>
       <c r="G21" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>17.850000000000001</v>
+        <v>32.113934999999998</v>
       </c>
       <c r="H21" s="49">
         <f t="shared" si="0"/>
-        <v>17.850000000000001</v>
+        <v>32.113934999999998</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="H23" s="49">
         <f>SUBTOTAL(9,H16:H22)</f>
-        <v>184.66697674418603</v>
+        <v>226.50785274418604</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2722,11 +2722,11 @@
       </c>
       <c r="G24" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H24" s="49">
         <f t="shared" si="0"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2778,11 +2778,11 @@
       </c>
       <c r="G26" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>17.850000000000001</v>
+        <v>32.113934999999998</v>
       </c>
       <c r="H26" s="49">
         <f t="shared" si="0"/>
-        <v>17.850000000000001</v>
+        <v>32.113934999999998</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2806,11 +2806,11 @@
       </c>
       <c r="G27" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.83</v>
+        <v>21.283352999999998</v>
       </c>
       <c r="H27" s="49">
         <f t="shared" si="0"/>
-        <v>11.83</v>
+        <v>21.283352999999998</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2834,11 +2834,11 @@
       </c>
       <c r="G28" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>16.309999999999999</v>
+        <v>29.343320999999996</v>
       </c>
       <c r="H28" s="49">
         <f t="shared" si="0"/>
-        <v>16.309999999999999</v>
+        <v>29.343320999999996</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2862,11 +2862,11 @@
       </c>
       <c r="G29" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
       <c r="H29" s="49">
         <f t="shared" si="0"/>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -2974,11 +2974,11 @@
       </c>
       <c r="G33" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>25.46</v>
+        <v>45.805086000000003</v>
       </c>
       <c r="H33" s="49">
         <f t="shared" si="0"/>
-        <v>25.46</v>
+        <v>45.805086000000003</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3002,11 +3002,11 @@
       </c>
       <c r="G34" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12.52</v>
+        <v>22.524731999999997</v>
       </c>
       <c r="H34" s="49">
         <f t="shared" si="0"/>
-        <v>12.52</v>
+        <v>22.524731999999997</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3030,11 +3030,11 @@
       </c>
       <c r="G35" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H35" s="49">
         <f t="shared" si="0"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3058,11 +3058,11 @@
       </c>
       <c r="G36" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>22.65</v>
+        <v>40.749614999999999</v>
       </c>
       <c r="H36" s="49">
         <f t="shared" si="0"/>
-        <v>22.65</v>
+        <v>40.749614999999999</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="H38" s="49">
         <f>SUBTOTAL(9,H24:H37)</f>
-        <v>379.6346511627907</v>
+        <v>474.87138916279071</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3132,11 +3132,11 @@
       </c>
       <c r="G39" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H39" s="49">
         <f t="shared" si="0"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3188,11 +3188,11 @@
       </c>
       <c r="G41" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>17.850000000000001</v>
+        <v>32.113934999999998</v>
       </c>
       <c r="H41" s="49">
         <f t="shared" si="0"/>
-        <v>17.850000000000001</v>
+        <v>32.113934999999998</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3216,11 +3216,11 @@
       </c>
       <c r="G42" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.83</v>
+        <v>21.283352999999998</v>
       </c>
       <c r="H42" s="49">
         <f t="shared" si="0"/>
-        <v>11.83</v>
+        <v>21.283352999999998</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3244,11 +3244,11 @@
       </c>
       <c r="G43" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>16.309999999999999</v>
+        <v>29.343320999999996</v>
       </c>
       <c r="H43" s="49">
         <f t="shared" si="0"/>
-        <v>16.309999999999999</v>
+        <v>29.343320999999996</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3272,11 +3272,11 @@
       </c>
       <c r="G44" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
       <c r="H44" s="49">
         <f t="shared" si="0"/>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3384,11 +3384,11 @@
       </c>
       <c r="G48" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>25.46</v>
+        <v>45.805086000000003</v>
       </c>
       <c r="H48" s="49">
         <f t="shared" si="0"/>
-        <v>25.46</v>
+        <v>45.805086000000003</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3412,11 +3412,11 @@
       </c>
       <c r="G49" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12.52</v>
+        <v>22.524731999999997</v>
       </c>
       <c r="H49" s="49">
         <f t="shared" si="0"/>
-        <v>12.52</v>
+        <v>22.524731999999997</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3440,11 +3440,11 @@
       </c>
       <c r="G50" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H50" s="49">
         <f t="shared" si="0"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3468,11 +3468,11 @@
       </c>
       <c r="G51" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>22.65</v>
+        <v>40.749614999999999</v>
       </c>
       <c r="H51" s="49">
         <f t="shared" si="0"/>
-        <v>22.65</v>
+        <v>40.749614999999999</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="H54" s="49">
         <f>SUBTOTAL(9,H39:H53)</f>
-        <v>481.89883720930231</v>
+        <v>577.13557520930226</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3570,11 +3570,11 @@
       </c>
       <c r="G55" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.97</v>
+        <v>8.9415269999999989</v>
       </c>
       <c r="H55" s="49">
         <f t="shared" si="0"/>
-        <v>4.97</v>
+        <v>8.9415269999999989</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3626,11 +3626,11 @@
       </c>
       <c r="G57" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>21.2</v>
+        <v>38.140919999999994</v>
       </c>
       <c r="H57" s="49">
         <f t="shared" si="0"/>
-        <v>21.2</v>
+        <v>38.140919999999994</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="H61" s="49">
         <f>SUBTOTAL(9,H55:H60)</f>
-        <v>203.82581395348836</v>
+        <v>224.73826095348835</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3756,11 +3756,11 @@
       </c>
       <c r="G62" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.97</v>
+        <v>8.9415269999999989</v>
       </c>
       <c r="H62" s="49">
         <f t="shared" si="0"/>
-        <v>4.97</v>
+        <v>8.9415269999999989</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3812,11 +3812,11 @@
       </c>
       <c r="G64" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>21.2</v>
+        <v>38.140919999999994</v>
       </c>
       <c r="H64" s="49">
         <f t="shared" si="0"/>
-        <v>21.2</v>
+        <v>38.140919999999994</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H68" s="49">
         <f>SUBTOTAL(9,H62:H67)</f>
-        <v>203.82581395348836</v>
+        <v>224.73826095348835</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3942,11 +3942,11 @@
       </c>
       <c r="G69" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.97</v>
+        <v>8.9415269999999989</v>
       </c>
       <c r="H69" s="49">
         <f t="shared" si="0"/>
-        <v>4.97</v>
+        <v>8.9415269999999989</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -3998,11 +3998,11 @@
       </c>
       <c r="G71" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>9.6199999999999992</v>
+        <v>17.307341999999998</v>
       </c>
       <c r="H71" s="49">
         <f t="shared" si="0"/>
-        <v>9.6199999999999992</v>
+        <v>17.307341999999998</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4026,11 +4026,11 @@
       </c>
       <c r="G72" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
       <c r="H72" s="49">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4054,11 +4054,11 @@
       </c>
       <c r="G73" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
       <c r="H73" s="49">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4082,11 +4082,11 @@
       </c>
       <c r="G74" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>41.69</v>
+        <v>75.004478999999989</v>
       </c>
       <c r="H74" s="49">
         <f t="shared" ref="H74:H143" si="1">E74*G74</f>
-        <v>41.69</v>
+        <v>75.004478999999989</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="12" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="H76" s="49">
         <f>SUBTOTAL(9,H69:H75)</f>
-        <v>212.58697674418602</v>
+        <v>276.73872474418602</v>
       </c>
     </row>
     <row r="77" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4156,11 +4156,11 @@
       </c>
       <c r="G77" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.97</v>
+        <v>8.9415269999999989</v>
       </c>
       <c r="H77" s="49">
         <f t="shared" si="1"/>
-        <v>4.97</v>
+        <v>8.9415269999999989</v>
       </c>
     </row>
     <row r="78" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4212,11 +4212,11 @@
       </c>
       <c r="G79" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>41.69</v>
+        <v>75.004478999999989</v>
       </c>
       <c r="H79" s="49">
         <f t="shared" si="1"/>
-        <v>41.69</v>
+        <v>75.004478999999989</v>
       </c>
     </row>
     <row r="80" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4240,11 +4240,11 @@
       </c>
       <c r="G80" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
       <c r="H80" s="49">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
     </row>
     <row r="81" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4268,11 +4268,11 @@
       </c>
       <c r="G81" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
       <c r="H81" s="49">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
     </row>
     <row r="82" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4296,11 +4296,11 @@
       </c>
       <c r="G82" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>21.2</v>
+        <v>38.140919999999994</v>
       </c>
       <c r="H82" s="49">
         <f t="shared" si="1"/>
-        <v>21.2</v>
+        <v>38.140919999999994</v>
       </c>
     </row>
     <row r="83" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4408,11 +4408,11 @@
       </c>
       <c r="G86" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>18.72</v>
+        <v>33.679151999999995</v>
       </c>
       <c r="H86" s="49">
         <f t="shared" si="1"/>
-        <v>18.72</v>
+        <v>33.679151999999995</v>
       </c>
     </row>
     <row r="87" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4436,11 +4436,11 @@
       </c>
       <c r="G87" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.21</v>
+        <v>20.167911</v>
       </c>
       <c r="H87" s="49">
         <f t="shared" si="1"/>
-        <v>11.21</v>
+        <v>20.167911</v>
       </c>
     </row>
     <row r="88" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4464,11 +4464,11 @@
       </c>
       <c r="G88" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>9.6199999999999992</v>
+        <v>17.307341999999998</v>
       </c>
       <c r="H88" s="49">
         <f t="shared" si="1"/>
-        <v>9.6199999999999992</v>
+        <v>17.307341999999998</v>
       </c>
     </row>
     <row r="89" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H90" s="49">
         <f>SUBTOTAL(9,H77:H89)</f>
-        <v>391.86465116279066</v>
+        <v>496.87438216279065</v>
       </c>
     </row>
     <row r="91" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4538,11 +4538,11 @@
       </c>
       <c r="G91" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.97</v>
+        <v>8.9415269999999989</v>
       </c>
       <c r="H91" s="49">
         <f t="shared" si="1"/>
-        <v>4.97</v>
+        <v>8.9415269999999989</v>
       </c>
     </row>
     <row r="92" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4594,11 +4594,11 @@
       </c>
       <c r="G93" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>41.69</v>
+        <v>75.004478999999989</v>
       </c>
       <c r="H93" s="49">
         <f t="shared" si="1"/>
-        <v>41.69</v>
+        <v>75.004478999999989</v>
       </c>
     </row>
     <row r="94" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4622,11 +4622,11 @@
       </c>
       <c r="G94" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
       <c r="H94" s="49">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
     </row>
     <row r="95" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4650,11 +4650,11 @@
       </c>
       <c r="G95" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
       <c r="H95" s="49">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
     </row>
     <row r="96" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4678,11 +4678,11 @@
       </c>
       <c r="G96" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>21.2</v>
+        <v>38.140919999999994</v>
       </c>
       <c r="H96" s="49">
         <f t="shared" si="1"/>
-        <v>21.2</v>
+        <v>38.140919999999994</v>
       </c>
     </row>
     <row r="97" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4790,11 +4790,11 @@
       </c>
       <c r="G100" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>18.72</v>
+        <v>33.679151999999995</v>
       </c>
       <c r="H100" s="49">
         <f t="shared" si="1"/>
-        <v>18.72</v>
+        <v>33.679151999999995</v>
       </c>
     </row>
     <row r="101" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4818,11 +4818,11 @@
       </c>
       <c r="G101" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.21</v>
+        <v>20.167911</v>
       </c>
       <c r="H101" s="49">
         <f t="shared" si="1"/>
-        <v>11.21</v>
+        <v>20.167911</v>
       </c>
     </row>
     <row r="102" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4846,11 +4846,11 @@
       </c>
       <c r="G102" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>9.6199999999999992</v>
+        <v>17.307341999999998</v>
       </c>
       <c r="H102" s="49">
         <f t="shared" si="1"/>
-        <v>9.6199999999999992</v>
+        <v>17.307341999999998</v>
       </c>
     </row>
     <row r="103" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="H105" s="49">
         <f>SUBTOTAL(9,H91:H104)</f>
-        <v>494.12883720930233</v>
+        <v>599.13856820930232</v>
       </c>
     </row>
     <row r="106" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -4948,11 +4948,11 @@
       </c>
       <c r="G106" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H106" s="49">
         <f t="shared" si="1"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="107" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5004,11 +5004,11 @@
       </c>
       <c r="G108" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
       <c r="H108" s="49">
         <f t="shared" si="1"/>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
     </row>
     <row r="109" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="H112" s="49">
         <f>SUBTOTAL(9,H106:H111)</f>
-        <v>281.69860465116278</v>
+        <v>290.23299265116282</v>
       </c>
     </row>
     <row r="113" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5134,11 +5134,11 @@
       </c>
       <c r="G113" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H113" s="49">
         <f t="shared" si="1"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="114" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5190,11 +5190,11 @@
       </c>
       <c r="G115" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
       <c r="H115" s="49">
         <f t="shared" si="1"/>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
     </row>
     <row r="116" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="H119" s="49">
         <f>SUBTOTAL(9,H113:H118)</f>
-        <v>281.69860465116278</v>
+        <v>290.23299265116282</v>
       </c>
     </row>
     <row r="120" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5320,11 +5320,11 @@
       </c>
       <c r="G120" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H120" s="49">
         <f t="shared" si="1"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="121" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5376,11 +5376,11 @@
       </c>
       <c r="G122" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
       <c r="H122" s="49">
         <f t="shared" si="1"/>
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
     </row>
     <row r="123" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5404,11 +5404,11 @@
       </c>
       <c r="G123" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
       <c r="H123" s="49">
         <f t="shared" si="1"/>
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
     </row>
     <row r="124" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5432,11 +5432,11 @@
       </c>
       <c r="G124" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
       <c r="H124" s="49">
         <f t="shared" si="1"/>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
     </row>
     <row r="125" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="G125" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H125" s="49">
         <f t="shared" si="1"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="126" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5488,11 +5488,11 @@
       </c>
       <c r="G126" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
       <c r="H126" s="49">
         <f t="shared" si="1"/>
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
     </row>
     <row r="127" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5516,11 +5516,11 @@
       </c>
       <c r="G127" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
       <c r="H127" s="49">
         <f t="shared" si="1"/>
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
     </row>
     <row r="128" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="H129" s="49">
         <f>SUBTOTAL(9,H120:H128)</f>
-        <v>213.43860465116279</v>
+        <v>274.82546665116274</v>
       </c>
     </row>
     <row r="130" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="G130" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H130" s="49">
         <f t="shared" si="1"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="131" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5646,11 +5646,11 @@
       </c>
       <c r="G132" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H132" s="49">
         <f t="shared" si="1"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="133" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5674,11 +5674,11 @@
       </c>
       <c r="G133" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
       <c r="H133" s="49">
         <f t="shared" si="1"/>
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
     </row>
     <row r="134" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5702,11 +5702,11 @@
       </c>
       <c r="G134" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
       <c r="H134" s="49">
         <f t="shared" si="1"/>
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
     </row>
     <row r="135" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5730,11 +5730,11 @@
       </c>
       <c r="G135" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
       <c r="H135" s="49">
         <f t="shared" si="1"/>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
     </row>
     <row r="136" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5758,11 +5758,11 @@
       </c>
       <c r="G136" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
       <c r="H136" s="49">
         <f t="shared" si="1"/>
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
     </row>
     <row r="137" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5786,11 +5786,11 @@
       </c>
       <c r="G137" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
       <c r="H137" s="49">
         <f t="shared" si="1"/>
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
     </row>
     <row r="138" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5814,11 +5814,11 @@
       </c>
       <c r="G138" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
       <c r="H138" s="49">
         <f t="shared" si="1"/>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
     </row>
     <row r="139" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5926,11 +5926,11 @@
       </c>
       <c r="G142" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>48.66</v>
+        <v>87.544205999999988</v>
       </c>
       <c r="H142" s="49">
         <f t="shared" si="1"/>
-        <v>48.66</v>
+        <v>87.544205999999988</v>
       </c>
     </row>
     <row r="143" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5954,11 +5954,11 @@
       </c>
       <c r="G143" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12.52</v>
+        <v>22.524731999999997</v>
       </c>
       <c r="H143" s="49">
         <f t="shared" si="1"/>
-        <v>12.52</v>
+        <v>22.524731999999997</v>
       </c>
     </row>
     <row r="144" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -5982,11 +5982,11 @@
       </c>
       <c r="G144" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>58.81</v>
+        <v>105.805071</v>
       </c>
       <c r="H144" s="49">
         <f t="shared" ref="H144:H213" si="2">E144*G144</f>
-        <v>58.81</v>
+        <v>105.805071</v>
       </c>
     </row>
     <row r="145" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="H146" s="49">
         <f>SUBTOTAL(9,H130:H145)</f>
-        <v>556.81744186046512</v>
+        <v>719.03474186046503</v>
       </c>
     </row>
     <row r="147" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6056,11 +6056,11 @@
       </c>
       <c r="G147" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H147" s="49">
         <f t="shared" si="2"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="148" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6112,11 +6112,11 @@
       </c>
       <c r="G149" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H149" s="49">
         <f t="shared" si="2"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="150" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6140,11 +6140,11 @@
       </c>
       <c r="G150" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
       <c r="H150" s="49">
         <f t="shared" si="2"/>
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
     </row>
     <row r="151" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6168,11 +6168,11 @@
       </c>
       <c r="G151" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
       <c r="H151" s="49">
         <f t="shared" si="2"/>
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
     </row>
     <row r="152" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6196,11 +6196,11 @@
       </c>
       <c r="G152" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
       <c r="H152" s="49">
         <f t="shared" si="2"/>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
     </row>
     <row r="153" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6224,11 +6224,11 @@
       </c>
       <c r="G153" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
       <c r="H153" s="49">
         <f t="shared" si="2"/>
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
     </row>
     <row r="154" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6252,11 +6252,11 @@
       </c>
       <c r="G154" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
       <c r="H154" s="49">
         <f t="shared" si="2"/>
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
     </row>
     <row r="155" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6280,11 +6280,11 @@
       </c>
       <c r="G155" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
       <c r="H155" s="49">
         <f t="shared" si="2"/>
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
     </row>
     <row r="156" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6392,11 +6392,11 @@
       </c>
       <c r="G159" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>48.66</v>
+        <v>87.544205999999988</v>
       </c>
       <c r="H159" s="49">
         <f t="shared" si="2"/>
-        <v>48.66</v>
+        <v>87.544205999999988</v>
       </c>
     </row>
     <row r="160" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6420,11 +6420,11 @@
       </c>
       <c r="G160" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12.52</v>
+        <v>22.524731999999997</v>
       </c>
       <c r="H160" s="49">
         <f t="shared" si="2"/>
-        <v>12.52</v>
+        <v>22.524731999999997</v>
       </c>
     </row>
     <row r="161" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6448,11 +6448,11 @@
       </c>
       <c r="G161" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>58.81</v>
+        <v>105.805071</v>
       </c>
       <c r="H161" s="49">
         <f t="shared" si="2"/>
-        <v>58.81</v>
+        <v>105.805071</v>
       </c>
     </row>
     <row r="162" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="H164" s="49">
         <f>SUBTOTAL(9,H147:H163)</f>
-        <v>761.34581395348835</v>
+        <v>923.56311395348825</v>
       </c>
     </row>
     <row r="165" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6550,11 +6550,11 @@
       </c>
       <c r="G165" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H165" s="49">
         <f t="shared" si="2"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="166" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="H171" s="49">
         <f>SUBTOTAL(9,H165:H170)</f>
-        <v>253.67046511627908</v>
+        <v>257.25842411627906</v>
       </c>
     </row>
     <row r="172" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6736,11 +6736,11 @@
       </c>
       <c r="G172" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H172" s="49">
         <f t="shared" si="2"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="173" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="H178" s="49">
         <f>SUBTOTAL(9,H172:H177)</f>
-        <v>253.67046511627908</v>
+        <v>257.25842411627906</v>
       </c>
     </row>
     <row r="179" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6920,11 +6920,11 @@
       </c>
       <c r="G179" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H179" s="49">
         <f t="shared" si="2"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="180" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6972,11 +6972,11 @@
       </c>
       <c r="G181" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
       <c r="H181" s="49">
         <f t="shared" si="2"/>
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
     </row>
     <row r="182" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6998,11 +6998,11 @@
       </c>
       <c r="G182" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
       <c r="H182" s="49">
         <f t="shared" si="2"/>
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
     </row>
     <row r="183" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7024,11 +7024,11 @@
       </c>
       <c r="G183" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
       <c r="H183" s="49">
         <f t="shared" si="2"/>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
     </row>
     <row r="184" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7050,11 +7050,11 @@
       </c>
       <c r="G184" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H184" s="49">
         <f t="shared" si="2"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="185" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7076,11 +7076,11 @@
       </c>
       <c r="G185" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
       <c r="H185" s="49">
         <f t="shared" si="2"/>
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
     </row>
     <row r="186" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7102,11 +7102,11 @@
       </c>
       <c r="G186" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
       <c r="H186" s="49">
         <f t="shared" si="2"/>
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
     </row>
     <row r="187" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="H188" s="49">
         <f>SUBTOTAL(9,H179:H187)</f>
-        <v>213.43860465116279</v>
+        <v>274.82546665116274</v>
       </c>
     </row>
     <row r="189" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7172,11 +7172,11 @@
       </c>
       <c r="G189" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H189" s="49">
         <f t="shared" si="2"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="190" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7224,11 +7224,11 @@
       </c>
       <c r="G191" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H191" s="49">
         <f t="shared" si="2"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="192" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7250,11 +7250,11 @@
       </c>
       <c r="G192" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
       <c r="H192" s="49">
         <f t="shared" si="2"/>
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
     </row>
     <row r="193" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7276,11 +7276,11 @@
       </c>
       <c r="G193" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
       <c r="H193" s="49">
         <f t="shared" si="2"/>
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
     </row>
     <row r="194" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7302,11 +7302,11 @@
       </c>
       <c r="G194" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
       <c r="H194" s="49">
         <f t="shared" si="2"/>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
     </row>
     <row r="195" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="G195" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
       <c r="H195" s="49">
         <f t="shared" si="2"/>
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
     </row>
     <row r="196" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7354,11 +7354,11 @@
       </c>
       <c r="G196" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
       <c r="H196" s="49">
         <f t="shared" si="2"/>
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
     </row>
     <row r="197" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7484,11 +7484,11 @@
       </c>
       <c r="G201" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>46.51</v>
+        <v>83.676140999999987</v>
       </c>
       <c r="H201" s="49">
         <f t="shared" si="2"/>
-        <v>46.51</v>
+        <v>83.676140999999987</v>
       </c>
     </row>
     <row r="202" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7510,11 +7510,11 @@
       </c>
       <c r="G202" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>14.83</v>
+        <v>26.680653</v>
       </c>
       <c r="H202" s="49">
         <f t="shared" si="2"/>
-        <v>14.83</v>
+        <v>26.680653</v>
       </c>
     </row>
     <row r="203" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="H204" s="49">
         <f>SUBTOTAL(9,H189:H203)</f>
-        <v>470.13930232558135</v>
+        <v>580.54295832558137</v>
       </c>
     </row>
     <row r="205" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7580,11 +7580,11 @@
       </c>
       <c r="G205" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="H205" s="49">
         <f t="shared" si="2"/>
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
     </row>
     <row r="206" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7632,11 +7632,11 @@
       </c>
       <c r="G207" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H207" s="49">
         <f t="shared" si="2"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="208" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7658,11 +7658,11 @@
       </c>
       <c r="G208" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
       <c r="H208" s="49">
         <f t="shared" si="2"/>
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
     </row>
     <row r="209" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7684,11 +7684,11 @@
       </c>
       <c r="G209" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
       <c r="H209" s="49">
         <f t="shared" si="2"/>
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
     </row>
     <row r="210" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7710,11 +7710,11 @@
       </c>
       <c r="G210" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
       <c r="H210" s="49">
         <f t="shared" si="2"/>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
     </row>
     <row r="211" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7736,11 +7736,11 @@
       </c>
       <c r="G211" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
       <c r="H211" s="49">
         <f t="shared" si="2"/>
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
     </row>
     <row r="212" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7762,11 +7762,11 @@
       </c>
       <c r="G212" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
       <c r="H212" s="49">
         <f t="shared" si="2"/>
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
     </row>
     <row r="213" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7892,11 +7892,11 @@
       </c>
       <c r="G217" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>46.51</v>
+        <v>83.676140999999987</v>
       </c>
       <c r="H217" s="49">
         <f t="shared" si="3"/>
-        <v>46.51</v>
+        <v>83.676140999999987</v>
       </c>
     </row>
     <row r="218" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7918,11 +7918,11 @@
       </c>
       <c r="G218" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>14.83</v>
+        <v>26.680653</v>
       </c>
       <c r="H218" s="49">
         <f t="shared" si="3"/>
-        <v>14.83</v>
+        <v>26.680653</v>
       </c>
     </row>
     <row r="219" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7970,11 +7970,11 @@
       </c>
       <c r="G220" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>72.239999999999995</v>
+        <v>129.966984</v>
       </c>
       <c r="H220" s="49">
         <f t="shared" si="3"/>
-        <v>72.239999999999995</v>
+        <v>129.966984</v>
       </c>
     </row>
     <row r="221" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="H222" s="49">
         <f>SUBTOTAL(9,H205:H221)</f>
-        <v>878.77465116279063</v>
+        <v>1046.9052911627907</v>
       </c>
     </row>
     <row r="223" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8040,11 +8040,11 @@
       </c>
       <c r="G223" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>30.95</v>
+        <v>55.682144999999998</v>
       </c>
       <c r="H223" s="49">
         <f t="shared" si="3"/>
-        <v>30.95</v>
+        <v>55.682144999999998</v>
       </c>
     </row>
     <row r="224" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="H229" s="49">
         <f>SUBTOTAL(9,H223:H228)</f>
-        <v>302.38395348837207</v>
+        <v>327.11609848837213</v>
       </c>
     </row>
     <row r="230" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8214,11 +8214,11 @@
       </c>
       <c r="G230" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>34.08</v>
+        <v>61.313327999999991</v>
       </c>
       <c r="H230" s="49">
         <f t="shared" si="3"/>
-        <v>34.08</v>
+        <v>61.313327999999991</v>
       </c>
     </row>
     <row r="231" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8240,11 +8240,11 @@
       </c>
       <c r="G231" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H231" s="49">
         <f t="shared" si="3"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="232" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8266,11 +8266,11 @@
       </c>
       <c r="G232" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.51</v>
+        <v>13.511240999999998</v>
       </c>
       <c r="H232" s="49">
         <f t="shared" si="3"/>
-        <v>7.51</v>
+        <v>13.511240999999998</v>
       </c>
     </row>
     <row r="233" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8292,11 +8292,11 @@
       </c>
       <c r="G233" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>22.53</v>
+        <v>40.533723000000002</v>
       </c>
       <c r="H233" s="49">
         <f t="shared" si="3"/>
-        <v>22.53</v>
+        <v>40.533723000000002</v>
       </c>
     </row>
     <row r="234" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="H235" s="49">
         <f>SUBTOTAL(9,H230:H234)</f>
-        <v>124.13953488372093</v>
+        <v>176.88013488372093</v>
       </c>
     </row>
     <row r="236" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8362,11 +8362,11 @@
       </c>
       <c r="G236" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>30.95</v>
+        <v>55.682144999999998</v>
       </c>
       <c r="H236" s="49">
         <f t="shared" si="3"/>
-        <v>30.95</v>
+        <v>55.682144999999998</v>
       </c>
     </row>
     <row r="237" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8414,11 +8414,11 @@
       </c>
       <c r="G238" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>34.08</v>
+        <v>61.313327999999991</v>
       </c>
       <c r="H238" s="49">
         <f t="shared" si="3"/>
-        <v>34.08</v>
+        <v>61.313327999999991</v>
       </c>
     </row>
     <row r="239" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8440,11 +8440,11 @@
       </c>
       <c r="G239" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>30.78</v>
+        <v>55.376297999999998</v>
       </c>
       <c r="H239" s="49">
         <f t="shared" si="3"/>
-        <v>30.78</v>
+        <v>55.376297999999998</v>
       </c>
     </row>
     <row r="240" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8466,11 +8466,11 @@
       </c>
       <c r="G240" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
       <c r="H240" s="49">
         <f t="shared" si="3"/>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
     </row>
     <row r="241" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8492,11 +8492,11 @@
       </c>
       <c r="G241" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H241" s="49">
         <f t="shared" si="3"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="242" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8518,11 +8518,11 @@
       </c>
       <c r="G242" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.51</v>
+        <v>13.511240999999998</v>
       </c>
       <c r="H242" s="49">
         <f t="shared" si="3"/>
-        <v>7.51</v>
+        <v>13.511240999999998</v>
       </c>
     </row>
     <row r="243" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8544,11 +8544,11 @@
       </c>
       <c r="G243" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>22.53</v>
+        <v>40.533723000000002</v>
       </c>
       <c r="H243" s="49">
         <f t="shared" si="3"/>
-        <v>22.53</v>
+        <v>40.533723000000002</v>
       </c>
     </row>
     <row r="244" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8570,11 +8570,11 @@
       </c>
       <c r="G244" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>28.84</v>
+        <v>51.886043999999998</v>
       </c>
       <c r="H244" s="49">
         <f t="shared" si="3"/>
-        <v>28.84</v>
+        <v>51.886043999999998</v>
       </c>
     </row>
     <row r="245" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8596,11 +8596,11 @@
       </c>
       <c r="G245" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>18</v>
+        <v>32.383800000000001</v>
       </c>
       <c r="H245" s="49">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>32.383800000000001</v>
       </c>
     </row>
     <row r="246" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="H247" s="49">
         <f>SUBTOTAL(9,H236:H246)</f>
-        <v>328.34162790697673</v>
+        <v>470.44558090697677</v>
       </c>
     </row>
     <row r="248" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8666,11 +8666,11 @@
       </c>
       <c r="G248" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>30.95</v>
+        <v>55.682144999999998</v>
       </c>
       <c r="H248" s="49">
         <f t="shared" si="3"/>
-        <v>30.95</v>
+        <v>55.682144999999998</v>
       </c>
     </row>
     <row r="249" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8718,11 +8718,11 @@
       </c>
       <c r="G250" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H250" s="49">
         <f t="shared" si="3"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="251" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8744,11 +8744,11 @@
       </c>
       <c r="G251" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>34.08</v>
+        <v>61.313327999999991</v>
       </c>
       <c r="H251" s="49">
         <f t="shared" si="3"/>
-        <v>34.08</v>
+        <v>61.313327999999991</v>
       </c>
     </row>
     <row r="252" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8770,11 +8770,11 @@
       </c>
       <c r="G252" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>30.78</v>
+        <v>55.376297999999998</v>
       </c>
       <c r="H252" s="49">
         <f t="shared" si="3"/>
-        <v>30.78</v>
+        <v>55.376297999999998</v>
       </c>
     </row>
     <row r="253" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8796,11 +8796,11 @@
       </c>
       <c r="G253" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
       <c r="H253" s="49">
         <f t="shared" si="3"/>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
     </row>
     <row r="254" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8822,11 +8822,11 @@
       </c>
       <c r="G254" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.51</v>
+        <v>13.511240999999998</v>
       </c>
       <c r="H254" s="49">
         <f t="shared" si="3"/>
-        <v>7.51</v>
+        <v>13.511240999999998</v>
       </c>
     </row>
     <row r="255" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8848,11 +8848,11 @@
       </c>
       <c r="G255" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>22.53</v>
+        <v>40.533723000000002</v>
       </c>
       <c r="H255" s="49">
         <f t="shared" si="3"/>
-        <v>22.53</v>
+        <v>40.533723000000002</v>
       </c>
     </row>
     <row r="256" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8874,11 +8874,11 @@
       </c>
       <c r="G256" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>28.84</v>
+        <v>51.886043999999998</v>
       </c>
       <c r="H256" s="49">
         <f t="shared" si="3"/>
-        <v>28.84</v>
+        <v>51.886043999999998</v>
       </c>
     </row>
     <row r="257" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8900,11 +8900,11 @@
       </c>
       <c r="G257" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>18</v>
+        <v>32.383800000000001</v>
       </c>
       <c r="H257" s="49">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>32.383800000000001</v>
       </c>
     </row>
     <row r="258" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9030,11 +9030,11 @@
       </c>
       <c r="G262" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>48.66</v>
+        <v>87.544205999999988</v>
       </c>
       <c r="H262" s="49">
         <f t="shared" si="3"/>
-        <v>48.66</v>
+        <v>87.544205999999988</v>
       </c>
     </row>
     <row r="263" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9056,11 +9056,11 @@
       </c>
       <c r="G263" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>14.83</v>
+        <v>26.680653</v>
       </c>
       <c r="H263" s="49">
         <f t="shared" si="3"/>
-        <v>14.83</v>
+        <v>26.680653</v>
       </c>
     </row>
     <row r="264" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="H265" s="49">
         <f>SUBTOTAL(9,H248:H264)</f>
-        <v>665.77720930232556</v>
+        <v>858.61602130232563</v>
       </c>
     </row>
     <row r="266" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9126,11 +9126,11 @@
       </c>
       <c r="G266" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>30.95</v>
+        <v>55.682144999999998</v>
       </c>
       <c r="H266" s="49">
         <f t="shared" si="3"/>
-        <v>30.95</v>
+        <v>55.682144999999998</v>
       </c>
     </row>
     <row r="267" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9178,11 +9178,11 @@
       </c>
       <c r="G268" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H268" s="49">
         <f t="shared" si="3"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="269" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9204,11 +9204,11 @@
       </c>
       <c r="G269" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>34.08</v>
+        <v>61.313327999999991</v>
       </c>
       <c r="H269" s="49">
         <f t="shared" si="3"/>
-        <v>34.08</v>
+        <v>61.313327999999991</v>
       </c>
     </row>
     <row r="270" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9230,11 +9230,11 @@
       </c>
       <c r="G270" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>30.78</v>
+        <v>55.376297999999998</v>
       </c>
       <c r="H270" s="49">
         <f t="shared" si="3"/>
-        <v>30.78</v>
+        <v>55.376297999999998</v>
       </c>
     </row>
     <row r="271" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9256,11 +9256,11 @@
       </c>
       <c r="G271" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
       <c r="H271" s="49">
         <f t="shared" si="3"/>
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
     </row>
     <row r="272" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9282,11 +9282,11 @@
       </c>
       <c r="G272" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.51</v>
+        <v>13.511240999999998</v>
       </c>
       <c r="H272" s="49">
         <f t="shared" si="3"/>
-        <v>7.51</v>
+        <v>13.511240999999998</v>
       </c>
     </row>
     <row r="273" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9308,11 +9308,11 @@
       </c>
       <c r="G273" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>22.53</v>
+        <v>40.533723000000002</v>
       </c>
       <c r="H273" s="49">
         <f t="shared" si="3"/>
-        <v>22.53</v>
+        <v>40.533723000000002</v>
       </c>
     </row>
     <row r="274" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9334,11 +9334,11 @@
       </c>
       <c r="G274" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>28.84</v>
+        <v>51.886043999999998</v>
       </c>
       <c r="H274" s="49">
         <f t="shared" si="3"/>
-        <v>28.84</v>
+        <v>51.886043999999998</v>
       </c>
     </row>
     <row r="275" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9360,11 +9360,11 @@
       </c>
       <c r="G275" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>18</v>
+        <v>32.383800000000001</v>
       </c>
       <c r="H275" s="49">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>32.383800000000001</v>
       </c>
     </row>
     <row r="276" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9490,11 +9490,11 @@
       </c>
       <c r="G280" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>48.66</v>
+        <v>87.544205999999988</v>
       </c>
       <c r="H280" s="49">
         <f t="shared" si="3"/>
-        <v>48.66</v>
+        <v>87.544205999999988</v>
       </c>
     </row>
     <row r="281" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9516,11 +9516,11 @@
       </c>
       <c r="G281" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>14.83</v>
+        <v>26.680653</v>
       </c>
       <c r="H281" s="49">
         <f t="shared" si="3"/>
-        <v>14.83</v>
+        <v>26.680653</v>
       </c>
     </row>
     <row r="282" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9568,11 +9568,11 @@
       </c>
       <c r="G283" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>72.239999999999995</v>
+        <v>129.966984</v>
       </c>
       <c r="H283" s="49">
         <f t="shared" ref="H283:H353" si="4">E283*G283</f>
-        <v>72.239999999999995</v>
+        <v>129.966984</v>
       </c>
     </row>
     <row r="284" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="H285" s="49">
         <f>SUBTOTAL(9,H266:H284)</f>
-        <v>1074.4125581395347</v>
+        <v>1324.978354139535</v>
       </c>
     </row>
     <row r="286" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9638,11 +9638,11 @@
       </c>
       <c r="G286" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>15.14</v>
+        <v>27.238374</v>
       </c>
       <c r="H286" s="49">
         <f t="shared" si="4"/>
-        <v>15.14</v>
+        <v>27.238374</v>
       </c>
     </row>
     <row r="287" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="H292" s="49">
         <f>SUBTOTAL(9,H286:H291)</f>
-        <v>308.64837209302323</v>
+        <v>320.74674609302326</v>
       </c>
     </row>
     <row r="293" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9812,11 +9812,11 @@
       </c>
       <c r="G293" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>15.14</v>
+        <v>27.238374</v>
       </c>
       <c r="H293" s="49">
         <f t="shared" si="4"/>
-        <v>15.14</v>
+        <v>27.238374</v>
       </c>
     </row>
     <row r="294" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9864,11 +9864,11 @@
       </c>
       <c r="G295" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>77.540000000000006</v>
+        <v>139.50221400000001</v>
       </c>
       <c r="H295" s="49">
         <f t="shared" si="4"/>
-        <v>77.540000000000006</v>
+        <v>139.50221400000001</v>
       </c>
     </row>
     <row r="296" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9890,11 +9890,11 @@
       </c>
       <c r="G296" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>78.099999999999994</v>
+        <v>140.50970999999998</v>
       </c>
       <c r="H296" s="49">
         <f t="shared" si="4"/>
-        <v>78.099999999999994</v>
+        <v>140.50970999999998</v>
       </c>
     </row>
     <row r="297" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9916,11 +9916,11 @@
       </c>
       <c r="G297" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H297" s="49">
         <f t="shared" si="4"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="298" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9942,11 +9942,11 @@
       </c>
       <c r="G298" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>51.82</v>
+        <v>93.229361999999995</v>
       </c>
       <c r="H298" s="49">
         <f t="shared" si="4"/>
-        <v>51.82</v>
+        <v>93.229361999999995</v>
       </c>
     </row>
     <row r="299" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9968,11 +9968,11 @@
       </c>
       <c r="G299" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>21.28</v>
+        <v>38.284848000000004</v>
       </c>
       <c r="H299" s="49">
         <f t="shared" si="4"/>
-        <v>21.28</v>
+        <v>38.284848000000004</v>
       </c>
     </row>
     <row r="300" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="H301" s="49">
         <f>SUBTOTAL(9,H293:H300)</f>
-        <v>406.81116279069772</v>
+        <v>603.19797879069768</v>
       </c>
     </row>
     <row r="302" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10038,11 +10038,11 @@
       </c>
       <c r="G302" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>15.14</v>
+        <v>27.238374</v>
       </c>
       <c r="H302" s="49">
         <f t="shared" si="4"/>
-        <v>15.14</v>
+        <v>27.238374</v>
       </c>
     </row>
     <row r="303" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10090,11 +10090,11 @@
       </c>
       <c r="G304" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H304" s="49">
         <f t="shared" si="4"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="305" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10116,11 +10116,11 @@
       </c>
       <c r="G305" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>77.540000000000006</v>
+        <v>139.50221400000001</v>
       </c>
       <c r="H305" s="49">
         <f t="shared" si="4"/>
-        <v>77.540000000000006</v>
+        <v>139.50221400000001</v>
       </c>
     </row>
     <row r="306" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10142,11 +10142,11 @@
       </c>
       <c r="G306" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>78.099999999999994</v>
+        <v>140.50970999999998</v>
       </c>
       <c r="H306" s="49">
         <f t="shared" si="4"/>
-        <v>78.099999999999994</v>
+        <v>140.50970999999998</v>
       </c>
     </row>
     <row r="307" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10168,11 +10168,11 @@
       </c>
       <c r="G307" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>8.09</v>
+        <v>14.554718999999999</v>
       </c>
       <c r="H307" s="49">
         <f t="shared" si="4"/>
-        <v>8.09</v>
+        <v>14.554718999999999</v>
       </c>
     </row>
     <row r="308" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10194,11 +10194,11 @@
       </c>
       <c r="G308" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>72.239999999999995</v>
+        <v>129.966984</v>
       </c>
       <c r="H308" s="49">
         <f t="shared" si="4"/>
-        <v>72.239999999999995</v>
+        <v>129.966984</v>
       </c>
     </row>
     <row r="309" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10220,11 +10220,11 @@
       </c>
       <c r="G309" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.58</v>
+        <v>8.2398779999999991</v>
       </c>
       <c r="H309" s="49">
         <f t="shared" si="4"/>
-        <v>4.58</v>
+        <v>8.2398779999999991</v>
       </c>
     </row>
     <row r="310" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10246,11 +10246,11 @@
       </c>
       <c r="G310" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12.98</v>
+        <v>23.352318</v>
       </c>
       <c r="H310" s="49">
         <f t="shared" si="4"/>
-        <v>12.98</v>
+        <v>23.352318</v>
       </c>
     </row>
     <row r="311" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10272,11 +10272,11 @@
       </c>
       <c r="G311" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>28.61</v>
+        <v>51.472251</v>
       </c>
       <c r="H311" s="49">
         <f t="shared" si="4"/>
-        <v>28.61</v>
+        <v>51.472251</v>
       </c>
     </row>
     <row r="312" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10298,11 +10298,11 @@
       </c>
       <c r="G312" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>51.82</v>
+        <v>93.229361999999995</v>
       </c>
       <c r="H312" s="49">
         <f t="shared" si="4"/>
-        <v>51.82</v>
+        <v>93.229361999999995</v>
       </c>
     </row>
     <row r="313" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10324,11 +10324,11 @@
       </c>
       <c r="G313" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>21.28</v>
+        <v>38.284848000000004</v>
       </c>
       <c r="H313" s="49">
         <f t="shared" si="4"/>
-        <v>21.28</v>
+        <v>38.284848000000004</v>
       </c>
     </row>
     <row r="314" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10454,11 +10454,11 @@
       </c>
       <c r="G318" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>24.45</v>
+        <v>43.987994999999998</v>
       </c>
       <c r="H318" s="49">
         <f t="shared" si="4"/>
-        <v>24.45</v>
+        <v>43.987994999999998</v>
       </c>
     </row>
     <row r="319" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10480,11 +10480,11 @@
       </c>
       <c r="G319" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>14.73</v>
+        <v>26.500743</v>
       </c>
       <c r="H319" s="49">
         <f t="shared" si="4"/>
-        <v>14.73</v>
+        <v>26.500743</v>
       </c>
     </row>
     <row r="320" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="H321" s="49">
         <f>SUBTOTAL(9,H302:H320)</f>
-        <v>857.97162790697678</v>
+        <v>1186.7533319069767</v>
       </c>
     </row>
     <row r="322" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10550,11 +10550,11 @@
       </c>
       <c r="G322" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>15.14</v>
+        <v>27.238374</v>
       </c>
       <c r="H322" s="49">
         <f t="shared" si="4"/>
-        <v>15.14</v>
+        <v>27.238374</v>
       </c>
     </row>
     <row r="323" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10602,11 +10602,11 @@
       </c>
       <c r="G324" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H324" s="49">
         <f t="shared" si="4"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="325" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10628,11 +10628,11 @@
       </c>
       <c r="G325" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>77.540000000000006</v>
+        <v>139.50221400000001</v>
       </c>
       <c r="H325" s="49">
         <f t="shared" si="4"/>
-        <v>77.540000000000006</v>
+        <v>139.50221400000001</v>
       </c>
     </row>
     <row r="326" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10654,11 +10654,11 @@
       </c>
       <c r="G326" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>78.099999999999994</v>
+        <v>140.50970999999998</v>
       </c>
       <c r="H326" s="49">
         <f t="shared" si="4"/>
-        <v>78.099999999999994</v>
+        <v>140.50970999999998</v>
       </c>
     </row>
     <row r="327" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10680,11 +10680,11 @@
       </c>
       <c r="G327" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>8.09</v>
+        <v>14.554718999999999</v>
       </c>
       <c r="H327" s="49">
         <f t="shared" si="4"/>
-        <v>8.09</v>
+        <v>14.554718999999999</v>
       </c>
     </row>
     <row r="328" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10706,11 +10706,11 @@
       </c>
       <c r="G328" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>72.239999999999995</v>
+        <v>129.966984</v>
       </c>
       <c r="H328" s="49">
         <f t="shared" si="4"/>
-        <v>72.239999999999995</v>
+        <v>129.966984</v>
       </c>
     </row>
     <row r="329" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10732,11 +10732,11 @@
       </c>
       <c r="G329" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.58</v>
+        <v>8.2398779999999991</v>
       </c>
       <c r="H329" s="49">
         <f t="shared" si="4"/>
-        <v>4.58</v>
+        <v>8.2398779999999991</v>
       </c>
     </row>
     <row r="330" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10758,11 +10758,11 @@
       </c>
       <c r="G330" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12.98</v>
+        <v>23.352318</v>
       </c>
       <c r="H330" s="49">
         <f t="shared" si="4"/>
-        <v>12.98</v>
+        <v>23.352318</v>
       </c>
     </row>
     <row r="331" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10784,11 +10784,11 @@
       </c>
       <c r="G331" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>28.61</v>
+        <v>51.472251</v>
       </c>
       <c r="H331" s="49">
         <f t="shared" si="4"/>
-        <v>28.61</v>
+        <v>51.472251</v>
       </c>
     </row>
     <row r="332" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10810,11 +10810,11 @@
       </c>
       <c r="G332" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>8.7899999999999991</v>
+        <v>15.814088999999997</v>
       </c>
       <c r="H332" s="49">
         <f t="shared" si="4"/>
-        <v>8.7899999999999991</v>
+        <v>15.814088999999997</v>
       </c>
     </row>
     <row r="333" spans="1:8" ht="15.75" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10836,11 +10836,11 @@
       </c>
       <c r="G333" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>110.51</v>
+        <v>198.81854100000001</v>
       </c>
       <c r="H333" s="49">
         <f t="shared" si="4"/>
-        <v>110.51</v>
+        <v>198.81854100000001</v>
       </c>
     </row>
     <row r="334" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10862,11 +10862,11 @@
       </c>
       <c r="G334" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>51.82</v>
+        <v>93.229361999999995</v>
       </c>
       <c r="H334" s="49">
         <f t="shared" si="4"/>
-        <v>51.82</v>
+        <v>93.229361999999995</v>
       </c>
     </row>
     <row r="335" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10888,11 +10888,11 @@
       </c>
       <c r="G335" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>21.28</v>
+        <v>38.284848000000004</v>
       </c>
       <c r="H335" s="49">
         <f t="shared" si="4"/>
-        <v>21.28</v>
+        <v>38.284848000000004</v>
       </c>
     </row>
     <row r="336" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10966,11 +10966,11 @@
       </c>
       <c r="G338" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.69</v>
+        <v>13.835079</v>
       </c>
       <c r="H338" s="49">
         <f t="shared" si="4"/>
-        <v>7.69</v>
+        <v>13.835079</v>
       </c>
     </row>
     <row r="339" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11044,11 +11044,11 @@
       </c>
       <c r="G341" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>24.45</v>
+        <v>43.987994999999998</v>
       </c>
       <c r="H341" s="49">
         <f t="shared" si="4"/>
-        <v>24.45</v>
+        <v>43.987994999999998</v>
       </c>
     </row>
     <row r="342" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11070,11 +11070,11 @@
       </c>
       <c r="G342" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>14.73</v>
+        <v>26.500743</v>
       </c>
       <c r="H342" s="49">
         <f t="shared" si="4"/>
-        <v>14.73</v>
+        <v>26.500743</v>
       </c>
     </row>
     <row r="343" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="H345" s="49">
         <f>SUBTOTAL(9,H322:H344)</f>
-        <v>1445.1504651162791</v>
+        <v>1875.4098781162793</v>
       </c>
     </row>
     <row r="346" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11262,11 +11262,11 @@
       </c>
       <c r="G350" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
       <c r="H350" s="49">
         <f t="shared" si="4"/>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
     </row>
     <row r="351" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="H352" s="49">
         <f>SUBTOTAL(9,H349:H351)</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
     </row>
     <row r="353" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11384,11 +11384,11 @@
       </c>
       <c r="G355" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.05</v>
+        <v>19.880054999999999</v>
       </c>
       <c r="H355" s="49">
         <f t="shared" si="5"/>
-        <v>11.05</v>
+        <v>19.880054999999999</v>
       </c>
     </row>
     <row r="356" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11410,11 +11410,11 @@
       </c>
       <c r="G356" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>5.08</v>
+        <v>9.1394280000000006</v>
       </c>
       <c r="H356" s="49">
         <f t="shared" si="5"/>
-        <v>5.08</v>
+        <v>9.1394280000000006</v>
       </c>
     </row>
     <row r="357" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11436,11 +11436,11 @@
       </c>
       <c r="G357" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
       <c r="H357" s="49">
         <f t="shared" si="5"/>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
     </row>
     <row r="358" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="H360" s="49">
         <f>SUBTOTAL(9,H353:H359)</f>
-        <v>187.17558139534884</v>
+        <v>206.0343413953488</v>
       </c>
     </row>
     <row r="361" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11628,11 +11628,11 @@
       </c>
       <c r="G365" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
       <c r="H365" s="49">
         <f t="shared" si="5"/>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
     </row>
     <row r="366" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="H367" s="49">
         <f>SUBTOTAL(9,H364:H366)</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
     </row>
     <row r="368" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11750,11 +11750,11 @@
       </c>
       <c r="G370" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
       <c r="H370" s="49">
         <f t="shared" si="5"/>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
     </row>
     <row r="371" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11776,11 +11776,11 @@
       </c>
       <c r="G371" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.05</v>
+        <v>19.880054999999999</v>
       </c>
       <c r="H371" s="49">
         <f t="shared" si="5"/>
-        <v>11.05</v>
+        <v>19.880054999999999</v>
       </c>
     </row>
     <row r="372" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11802,11 +11802,11 @@
       </c>
       <c r="G372" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>5.08</v>
+        <v>9.1394280000000006</v>
       </c>
       <c r="H372" s="49">
         <f t="shared" si="5"/>
-        <v>5.08</v>
+        <v>9.1394280000000006</v>
       </c>
     </row>
     <row r="373" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="H375" s="49">
         <f>SUBTOTAL(9,H368:H374)</f>
-        <v>187.17558139534884</v>
+        <v>206.0343413953488</v>
       </c>
     </row>
     <row r="376" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11994,11 +11994,11 @@
       </c>
       <c r="G380" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
       <c r="H380" s="49">
         <f t="shared" si="5"/>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
     </row>
     <row r="381" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="H382" s="49">
         <f>SUBTOTAL(9,H379:H381)</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
     </row>
     <row r="383" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12116,11 +12116,11 @@
       </c>
       <c r="G385" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
       <c r="H385" s="49">
         <f t="shared" si="5"/>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
     </row>
     <row r="386" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12142,11 +12142,11 @@
       </c>
       <c r="G386" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.05</v>
+        <v>19.880054999999999</v>
       </c>
       <c r="H386" s="49">
         <f t="shared" si="5"/>
-        <v>11.05</v>
+        <v>19.880054999999999</v>
       </c>
     </row>
     <row r="387" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12168,11 +12168,11 @@
       </c>
       <c r="G387" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>5.08</v>
+        <v>9.1394280000000006</v>
       </c>
       <c r="H387" s="49">
         <f t="shared" si="5"/>
-        <v>5.08</v>
+        <v>9.1394280000000006</v>
       </c>
     </row>
     <row r="388" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="H390" s="49">
         <f>SUBTOTAL(9,H383:H389)</f>
-        <v>191.39999999999998</v>
+        <v>210.25876</v>
       </c>
     </row>
     <row r="391" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12360,11 +12360,11 @@
       </c>
       <c r="G395" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.78</v>
+        <v>8.5996980000000001</v>
       </c>
       <c r="H395" s="49">
         <f t="shared" si="5"/>
-        <v>4.78</v>
+        <v>8.5996980000000001</v>
       </c>
     </row>
     <row r="396" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="H397" s="49">
         <f>SUBTOTAL(9,H394:H396)</f>
-        <v>81.942790697674411</v>
+        <v>85.762488697674414</v>
       </c>
     </row>
     <row r="398" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12482,11 +12482,11 @@
       </c>
       <c r="G400" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>4.78</v>
+        <v>8.5996980000000001</v>
       </c>
       <c r="H400" s="49">
         <f t="shared" si="5"/>
-        <v>4.78</v>
+        <v>8.5996980000000001</v>
       </c>
     </row>
     <row r="401" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12508,11 +12508,11 @@
       </c>
       <c r="G401" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>6.29</v>
+        <v>11.316338999999999</v>
       </c>
       <c r="H401" s="49">
         <f t="shared" si="5"/>
-        <v>6.29</v>
+        <v>11.316338999999999</v>
       </c>
     </row>
     <row r="402" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12534,11 +12534,11 @@
       </c>
       <c r="G402" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H402" s="49">
         <f t="shared" si="5"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="403" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="H405" s="49">
         <f>SUBTOTAL(9,H398:H404)</f>
-        <v>214.6701395348837</v>
+        <v>225.0184845348837</v>
       </c>
     </row>
     <row r="406" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12726,11 +12726,11 @@
       </c>
       <c r="G410" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
       <c r="H410" s="49">
         <f t="shared" si="5"/>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
     </row>
     <row r="411" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="H412" s="49">
         <f>SUBTOTAL(9,H409:H411)</f>
-        <v>84.632790697674409</v>
+        <v>90.602067697674414</v>
       </c>
     </row>
     <row r="413" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12848,11 +12848,11 @@
       </c>
       <c r="G415" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
       <c r="H415" s="49">
         <f t="shared" si="5"/>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
     </row>
     <row r="416" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12874,11 +12874,11 @@
       </c>
       <c r="G416" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>6.29</v>
+        <v>11.316338999999999</v>
       </c>
       <c r="H416" s="49">
         <f t="shared" si="5"/>
-        <v>6.29</v>
+        <v>11.316338999999999</v>
       </c>
     </row>
     <row r="417" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="H419" s="49">
         <f>SUBTOTAL(9,H413:H418)</f>
-        <v>215.4801395348837</v>
+        <v>226.47575553488372</v>
       </c>
     </row>
     <row r="420" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -12973,7 +12973,7 @@
         <v>3.6976744186046511</v>
       </c>
       <c r="H420" s="49">
-        <f t="shared" ref="H420:H433" si="6">E420*G420</f>
+        <f t="shared" ref="H420:H421" si="6">E420*G420</f>
         <v>7.3953488372093021</v>
       </c>
     </row>
@@ -13043,7 +13043,7 @@
         <v>3.6976744186046511</v>
       </c>
       <c r="H423" s="49">
-        <f t="shared" ref="H423:H433" si="7">E423*G423</f>
+        <f t="shared" ref="H423:H425" si="7">E423*G423</f>
         <v>7.3953488372093021</v>
       </c>
     </row>
@@ -13066,11 +13066,11 @@
       </c>
       <c r="G424" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
       <c r="H424" s="49">
         <f t="shared" si="7"/>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
     </row>
     <row r="425" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="H426" s="49">
         <f>SUBTOTAL(9,H423:H425)</f>
-        <v>84.632790697674409</v>
+        <v>90.602067697674414</v>
       </c>
     </row>
     <row r="427" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13139,7 +13139,7 @@
         <v>3.6976744186046511</v>
       </c>
       <c r="H427" s="49">
-        <f t="shared" ref="H427:H433" si="8">E427*G427</f>
+        <f t="shared" ref="H427:H432" si="8">E427*G427</f>
         <v>7.3953488372093021</v>
       </c>
     </row>
@@ -13188,11 +13188,11 @@
       </c>
       <c r="G429" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
       <c r="H429" s="49">
         <f t="shared" si="8"/>
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
     </row>
     <row r="430" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13214,11 +13214,11 @@
       </c>
       <c r="G430" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>6.29</v>
+        <v>11.316338999999999</v>
       </c>
       <c r="H430" s="49">
         <f t="shared" si="8"/>
-        <v>6.29</v>
+        <v>11.316338999999999</v>
       </c>
     </row>
     <row r="431" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="H433" s="49">
         <f>SUBTOTAL(9,H427:H432)</f>
-        <v>215.4801395348837</v>
+        <v>226.47575553488372</v>
       </c>
     </row>
     <row r="434" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13406,11 +13406,11 @@
       </c>
       <c r="G438" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>27.79</v>
+        <v>49.996988999999999</v>
       </c>
       <c r="H438" s="49">
         <f t="shared" si="5"/>
-        <v>27.79</v>
+        <v>49.996988999999999</v>
       </c>
     </row>
     <row r="439" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="H440" s="49">
         <f>SUBTOTAL(9,H437:H439)</f>
-        <v>104.95279069767442</v>
+        <v>127.15977969767442</v>
       </c>
     </row>
     <row r="441" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13528,11 +13528,11 @@
       </c>
       <c r="G443" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>27.79</v>
+        <v>49.996988999999999</v>
       </c>
       <c r="H443" s="49">
         <f t="shared" si="5"/>
-        <v>27.79</v>
+        <v>49.996988999999999</v>
       </c>
     </row>
     <row r="444" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13554,11 +13554,11 @@
       </c>
       <c r="G444" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>6.29</v>
+        <v>11.316338999999999</v>
       </c>
       <c r="H444" s="49">
         <f t="shared" si="5"/>
-        <v>6.29</v>
+        <v>11.316338999999999</v>
       </c>
     </row>
     <row r="445" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13580,11 +13580,11 @@
       </c>
       <c r="G445" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H445" s="49">
         <f t="shared" si="5"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="446" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="H448" s="49">
         <f>SUBTOTAL(9,H441:H447)</f>
-        <v>237.68013953488369</v>
+        <v>266.41577553488366</v>
       </c>
     </row>
     <row r="449" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13772,11 +13772,11 @@
       </c>
       <c r="G453" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>8.83</v>
+        <v>15.886052999999999</v>
       </c>
       <c r="H453" s="49">
         <f t="shared" si="9"/>
-        <v>8.83</v>
+        <v>15.886052999999999</v>
       </c>
     </row>
     <row r="454" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="H455" s="49">
         <f>SUBTOTAL(9,H452:H454)</f>
-        <v>89.690465116279057</v>
+        <v>96.746518116279063</v>
       </c>
     </row>
     <row r="456" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13894,11 +13894,11 @@
       </c>
       <c r="G458" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>8.83</v>
+        <v>15.886052999999999</v>
       </c>
       <c r="H458" s="49">
         <f t="shared" si="9"/>
-        <v>8.83</v>
+        <v>15.886052999999999</v>
       </c>
     </row>
     <row r="459" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13920,11 +13920,11 @@
       </c>
       <c r="G459" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>12.52</v>
+        <v>22.524731999999997</v>
       </c>
       <c r="H459" s="49">
         <f t="shared" si="9"/>
-        <v>12.52</v>
+        <v>22.524731999999997</v>
       </c>
     </row>
     <row r="460" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13946,11 +13946,11 @@
       </c>
       <c r="G460" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="H460" s="49">
         <f t="shared" si="9"/>
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
     </row>
     <row r="461" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="H463" s="49">
         <f>SUBTOTAL(9,H456:H462)</f>
-        <v>265.70441860465121</v>
+        <v>284.26751160465119</v>
       </c>
     </row>
     <row r="464" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -14138,11 +14138,11 @@
       </c>
       <c r="G468" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>37.409999999999997</v>
+        <v>67.304330999999991</v>
       </c>
       <c r="H468" s="49">
         <f t="shared" si="9"/>
-        <v>37.409999999999997</v>
+        <v>67.304330999999991</v>
       </c>
     </row>
     <row r="469" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -14164,11 +14164,11 @@
       </c>
       <c r="G469" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.21</v>
+        <v>20.167911</v>
       </c>
       <c r="H469" s="49">
         <f t="shared" si="9"/>
-        <v>11.21</v>
+        <v>20.167911</v>
       </c>
     </row>
     <row r="470" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -14190,11 +14190,11 @@
       </c>
       <c r="G470" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>9.6199999999999992</v>
+        <v>17.307341999999998</v>
       </c>
       <c r="H470" s="49">
         <f t="shared" si="9"/>
-        <v>9.6199999999999992</v>
+        <v>17.307341999999998</v>
       </c>
     </row>
     <row r="471" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -14238,7 +14238,7 @@
       </c>
       <c r="H472" s="49">
         <f>SUBTOTAL(9,H467:H471)</f>
-        <v>150.79813953488372</v>
+        <v>197.33772353488371</v>
       </c>
     </row>
     <row r="473" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -14312,11 +14312,11 @@
       </c>
       <c r="G475" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>37.409999999999997</v>
+        <v>67.304330999999991</v>
       </c>
       <c r="H475" s="49">
         <f t="shared" si="9"/>
-        <v>37.409999999999997</v>
+        <v>67.304330999999991</v>
       </c>
     </row>
     <row r="476" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -14338,11 +14338,11 @@
       </c>
       <c r="G476" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>11.21</v>
+        <v>20.167911</v>
       </c>
       <c r="H476" s="49">
         <f t="shared" si="9"/>
-        <v>11.21</v>
+        <v>20.167911</v>
       </c>
     </row>
     <row r="477" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -14364,11 +14364,11 @@
       </c>
       <c r="G477" s="49">
         <f>VLOOKUP(C:C,yedekparca!A:D,3,0)</f>
-        <v>9.6199999999999992</v>
+        <v>17.307341999999998</v>
       </c>
       <c r="H477" s="49">
         <f t="shared" si="9"/>
-        <v>9.6199999999999992</v>
+        <v>17.307341999999998</v>
       </c>
     </row>
     <row r="478" spans="1:8" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="H480" s="49">
         <f>SUBTOTAL(9,H473:H479)</f>
-        <v>280.11813953488377</v>
+        <v>326.6577235348837</v>
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.25">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="H481" s="49">
         <f>SUBTOTAL(9,H2:H479)</f>
-        <v>16039.586604651186</v>
+        <v>19277.683642651216</v>
       </c>
     </row>
   </sheetData>
@@ -14528,7 +14528,7 @@
       </c>
       <c r="D2" s="40">
         <f>bakimrecete!H8</f>
-        <v>188.33581395348835</v>
+        <v>196.87020195348836</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -14538,7 +14538,7 @@
       </c>
       <c r="I2" s="40">
         <f>D2*E2+D3*E3+D4*E4+D5*E5+D6*E6</f>
-        <v>2172.546511627907</v>
+        <v>2489.3736796279068</v>
       </c>
       <c r="J2" s="21" t="s">
         <v>396</v>
@@ -14552,7 +14552,7 @@
       </c>
       <c r="D3" s="40">
         <f>bakimrecete!H15</f>
-        <v>188.33581395348835</v>
+        <v>196.87020195348836</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="I3" s="40">
         <f>D31*E31+D32*E32+D33*E33+D34*E34+D35*E35</f>
-        <v>3113.51976744186</v>
+        <v>3584.4933254418602</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>396</v>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="D4" s="40">
         <f>bakimrecete!H23</f>
-        <v>184.66697674418603</v>
+        <v>226.50785274418604</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="I4" s="40">
         <f>D60*E60+D61*E61+D62*E62+D63*E63+D64*E64</f>
-        <v>6140.9679069767444</v>
+        <v>7074.3806349767437</v>
       </c>
       <c r="J4" s="21" t="s">
         <v>396</v>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="D5" s="40">
         <f>bakimrecete!H38</f>
-        <v>379.6346511627907</v>
+        <v>474.87138916279071</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="I5" s="40">
         <f>D89*E89+D90*E90+D91*E91+D92*E92+D93*E93</f>
-        <v>9066.1518604651155</v>
+        <v>10462.003758465116</v>
       </c>
       <c r="J5" s="21" t="s">
         <v>396</v>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="D6" s="40">
         <f>bakimrecete!H54</f>
-        <v>481.89883720930231</v>
+        <v>577.13557520930226</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="I6" s="40">
         <f>D7*E7+D8*E8+D9*E9+D10*E10</f>
-        <v>1836.1676744186047</v>
+        <v>2174.0431364186043</v>
       </c>
       <c r="J6" s="21" t="s">
         <v>108</v>
@@ -14652,7 +14652,7 @@
       </c>
       <c r="D7" s="40">
         <f>bakimrecete!H61</f>
-        <v>203.82581395348836</v>
+        <v>224.73826095348835</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -14662,7 +14662,7 @@
       </c>
       <c r="I7" s="40">
         <f>D36*E36+D37*E37+D38*E38+D39*E39+D40*E40</f>
-        <v>3342.3997674418606</v>
+        <v>3996.27133344186</v>
       </c>
       <c r="J7" s="21" t="s">
         <v>108</v>
@@ -14676,7 +14676,7 @@
       </c>
       <c r="D8" s="40">
         <f>bakimrecete!H68</f>
-        <v>203.82581395348836</v>
+        <v>224.73826095348835</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -14686,7 +14686,7 @@
       </c>
       <c r="I8" s="40">
         <f>D65*E65+D66*E66+D67*E67+D68*E68+D69*E69</f>
-        <v>6583.237906976743</v>
+        <v>7870.0685919767438</v>
       </c>
       <c r="J8" s="21" t="s">
         <v>108</v>
@@ -14700,7 +14700,7 @@
       </c>
       <c r="D9" s="40">
         <f>bakimrecete!H76</f>
-        <v>212.58697674418602</v>
+        <v>276.73872474418602</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -14710,7 +14710,7 @@
       </c>
       <c r="I9" s="40">
         <f>D94*E94+D95*E95+D96*E96+D97*E97+D98*E98</f>
-        <v>9721.8118604651154</v>
+        <v>11641.601664465114</v>
       </c>
       <c r="J9" s="21" t="s">
         <v>108</v>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="D10" s="40">
         <f>bakimrecete!H90</f>
-        <v>391.86465116279066</v>
+        <v>496.87438216279065</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="I10" s="40">
         <f>D12*E12+D13*E13+D14*E14+D15*E15+D16*E16</f>
-        <v>3153.533488372093</v>
+        <v>3643.4137523720929</v>
       </c>
       <c r="J10" s="21" t="s">
         <v>109</v>
@@ -14748,7 +14748,7 @@
       </c>
       <c r="D11" s="40">
         <f>bakimrecete!H105</f>
-        <v>494.12883720930233</v>
+        <v>599.13856820930232</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -14758,7 +14758,7 @@
       </c>
       <c r="I11" s="40">
         <f>D41*E41+D42*E42+D43*E43+D44*E44+D45*E45</f>
-        <v>4487.1867441860468</v>
+        <v>5217.7399461860459</v>
       </c>
       <c r="J11" s="21" t="s">
         <v>109</v>
@@ -14776,7 +14776,7 @@
       </c>
       <c r="D12" s="40">
         <f>bakimrecete!H112</f>
-        <v>281.69860465116278</v>
+        <v>290.23299265116282</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="I12" s="40">
         <f>D70*E70+D71*E71+D72*E72+D73*E73+D74*E74</f>
-        <v>8897.2032558139545</v>
+        <v>10349.775271813953</v>
       </c>
       <c r="J12" s="21" t="s">
         <v>109</v>
@@ -14800,7 +14800,7 @@
       </c>
       <c r="D13" s="40">
         <f>bakimrecete!H119</f>
-        <v>281.69860465116278</v>
+        <v>290.23299265116282</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="I13" s="40">
         <f>D99*E99+D100*E100+D101*E101+D102*E102+D103*E103</f>
-        <v>13102.691395348837</v>
+        <v>15277.282225348838</v>
       </c>
       <c r="J13" s="21" t="s">
         <v>109</v>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="D14" s="40">
         <f>bakimrecete!H129</f>
-        <v>213.43860465116279</v>
+        <v>274.82546665116274</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="I14" s="40">
         <f>D17*E17+D18*E18+D19*E19+D20*E20+D21*E21</f>
-        <v>3044.1434883720931</v>
+        <v>3463.3913033720928</v>
       </c>
       <c r="J14" s="21" t="s">
         <v>110</v>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="D15" s="40">
         <f>bakimrecete!H146</f>
-        <v>556.81744186046512</v>
+        <v>719.03474186046503</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="I15" s="40">
         <f>D46*E46+D47*E47+D48*E48+D49*E49+D50*E50</f>
-        <v>3993.6711627906975</v>
+        <v>4938.6788317906967</v>
       </c>
       <c r="J15" s="21" t="s">
         <v>110</v>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="D16" s="40">
         <f>bakimrecete!H164</f>
-        <v>761.34581395348835</v>
+        <v>923.56311395348825</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="I16" s="40">
         <f>D75*E75+D76*E76+D77*E77+D78*E78+D79*E79</f>
-        <v>8625.0895348837203</v>
+        <v>9875.6570618837213</v>
       </c>
       <c r="J16" s="21" t="s">
         <v>110</v>
@@ -14900,7 +14900,7 @@
       </c>
       <c r="D17" s="40">
         <f>bakimrecete!H171</f>
-        <v>253.67046511627908</v>
+        <v>257.25842411627906</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="I17" s="40">
         <f>D104*E104+D105*E105+D106*E106+D107*E107+D108*E108</f>
-        <v>12606.481395348837</v>
+        <v>14451.675214348837</v>
       </c>
       <c r="J17" s="21" t="s">
         <v>110</v>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="D18" s="40">
         <f>bakimrecete!H178</f>
-        <v>253.67046511627908</v>
+        <v>257.25842411627906</v>
       </c>
       <c r="E18">
         <v>4</v>
@@ -14934,7 +14934,7 @@
       </c>
       <c r="I18" s="40">
         <f>D22*E22+D23*E23+D24*E24+D25*E25+D26*E26</f>
-        <v>3195.8151162790696</v>
+        <v>4159.1221752790698</v>
       </c>
       <c r="J18" s="21" t="s">
         <v>111</v>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="D19" s="40">
         <f>bakimrecete!H188</f>
-        <v>213.43860465116279</v>
+        <v>274.82546665116274</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -14958,7 +14958,7 @@
       </c>
       <c r="I19" s="40">
         <f>D51*E51+D52*E52+D53*E53+D54*E54+D55*E55</f>
-        <v>4438.2130232558138</v>
+        <v>5841.9440472558144</v>
       </c>
       <c r="J19" s="21" t="s">
         <v>111</v>
@@ -14972,7 +14972,7 @@
       </c>
       <c r="D20" s="40">
         <f>bakimrecete!H204</f>
-        <v>470.13930232558135</v>
+        <v>580.54295832558137</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="I20" s="40">
         <f>D80*E80+D81*E81+D82*E82+D83*E83+D84*E84</f>
-        <v>8982.6774418604655</v>
+        <v>11823.134328860466</v>
       </c>
       <c r="J20" s="21" t="s">
         <v>111</v>
@@ -14996,7 +14996,7 @@
       </c>
       <c r="D21" s="40">
         <f>bakimrecete!H222</f>
-        <v>878.77465116279063</v>
+        <v>1046.9052911627907</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -15006,7 +15006,7 @@
       </c>
       <c r="I21" s="40">
         <f>D109*E109+D110*E110+D111*E111+D112*E112+D113*E113</f>
-        <v>13118.506511627906</v>
+        <v>17337.962277627907</v>
       </c>
       <c r="J21" s="21" t="s">
         <v>111</v>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="D22" s="40">
         <f>bakimrecete!H229</f>
-        <v>302.38395348837207</v>
+        <v>327.11609848837213</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="I22" s="40">
         <f>D27*E27+D28*E28+D29*E29+D30*E30</f>
-        <v>4283.3644186046513</v>
+        <v>5776.0592456046506</v>
       </c>
       <c r="J22" s="21" t="s">
         <v>112</v>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="D23" s="40">
         <f>bakimrecete!H235</f>
-        <v>124.13953488372093</v>
+        <v>176.88013488372093</v>
       </c>
       <c r="E23">
         <v>4</v>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="I23" s="40">
         <f>D56*E56+D57*E57+D58*E58+D59*E59</f>
-        <v>4690.1755813953496</v>
+        <v>6379.2572243953491</v>
       </c>
       <c r="J23" s="21" t="s">
         <v>112</v>
@@ -15072,7 +15072,7 @@
       </c>
       <c r="D24" s="40">
         <f>bakimrecete!H247</f>
-        <v>328.34162790697673</v>
+        <v>470.44558090697677</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="I24" s="40">
         <f>D85*E85+D86*E86+D87*E87+D88*E88</f>
-        <v>8800.91</v>
+        <v>11939.670917000001</v>
       </c>
       <c r="J24" s="21" t="s">
         <v>112</v>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="D25" s="40">
         <f>bakimrecete!H265</f>
-        <v>665.77720930232556</v>
+        <v>858.61602130232563</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -15106,7 +15106,7 @@
       </c>
       <c r="I25" s="40">
         <f>D114*E114+D115*E115+D116*E116+D117*E117</f>
-        <v>14040.408837209303</v>
+        <v>19184.934727209304</v>
       </c>
       <c r="J25" s="21" t="s">
         <v>112</v>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="D26" s="40">
         <f>bakimrecete!H285</f>
-        <v>1074.4125581395347</v>
+        <v>1324.978354139535</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="I26" s="40">
         <f>D118*E118+D119*E119+D120*E120</f>
-        <v>391.78511627906977</v>
+        <v>416.61315327906971</v>
       </c>
       <c r="J26" s="21" t="s">
         <v>187</v>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="D27" s="40">
         <f>bakimrecete!H292</f>
-        <v>308.64837209302323</v>
+        <v>320.74674609302326</v>
       </c>
       <c r="E27" s="9">
         <v>1</v>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="I27" s="40">
         <f>D142*E142+D143*E143+D144*E144</f>
-        <v>534.55744186046513</v>
+        <v>565.35475586046505</v>
       </c>
       <c r="J27" s="21" t="s">
         <v>187</v>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="D28" s="40">
         <f>bakimrecete!H301</f>
-        <v>406.81116279069772</v>
+        <v>603.19797879069768</v>
       </c>
       <c r="E28" s="35">
         <v>2</v>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="I28" s="40">
         <f>D166*E166+D167*E167+D168*E168</f>
-        <v>1094.4202325581396</v>
+        <v>1162.9350665581396</v>
       </c>
       <c r="J28" s="21" t="s">
         <v>187</v>
@@ -15196,7 +15196,7 @@
       </c>
       <c r="D29" s="40">
         <f>bakimrecete!H321</f>
-        <v>857.97162790697678</v>
+        <v>1186.7533319069767</v>
       </c>
       <c r="E29" s="35">
         <v>2</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I29" s="40">
         <f>D193*E193+D194*E194+D195*E195</f>
-        <v>1709.9127906976744</v>
+        <v>1815.1942156976743</v>
       </c>
       <c r="J29" s="21" t="s">
         <v>187</v>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="D30" s="40">
         <f>bakimrecete!H345</f>
-        <v>1445.1504651162791</v>
+        <v>1875.4098781162793</v>
       </c>
       <c r="E30" s="35">
         <v>1</v>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="I30" s="40">
         <f>D121*E121+D122*E122+D123*E123</f>
-        <v>391.78511627906977</v>
+        <v>416.61315327906971</v>
       </c>
       <c r="J30" s="21" t="s">
         <v>188</v>
@@ -15248,7 +15248,7 @@
       </c>
       <c r="D31" s="40">
         <f>bakimrecete!H8</f>
-        <v>188.33581395348835</v>
+        <v>196.87020195348836</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="I31" s="40">
         <f>D145*E145+D146*E146+D147*E147</f>
-        <v>534.55744186046513</v>
+        <v>565.35475586046505</v>
       </c>
       <c r="J31" s="21" t="s">
         <v>188</v>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="D32" s="40">
         <f>bakimrecete!H15</f>
-        <v>188.33581395348835</v>
+        <v>196.87020195348836</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="I32" s="40">
         <f>D169*E169+D170*E170+D171*E171</f>
-        <v>1094.4202325581396</v>
+        <v>1162.9350665581396</v>
       </c>
       <c r="J32" s="21" t="s">
         <v>188</v>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="D33" s="40">
         <f>bakimrecete!H23</f>
-        <v>184.66697674418603</v>
+        <v>226.50785274418604</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="I33" s="40">
         <f>D193*E193+D194*E194+D195*E195</f>
-        <v>1709.9127906976744</v>
+        <v>1815.1942156976743</v>
       </c>
       <c r="J33" s="21" t="s">
         <v>188</v>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="D34" s="40">
         <f>bakimrecete!H38</f>
-        <v>379.6346511627907</v>
+        <v>474.87138916279071</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="I34" s="40">
         <f>D124*E124+D125*E125+D126*E126</f>
-        <v>396.0095348837209</v>
+        <v>420.8375718837209</v>
       </c>
       <c r="J34" s="21" t="s">
         <v>190</v>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="D35" s="40">
         <f>bakimrecete!H54</f>
-        <v>481.89883720930231</v>
+        <v>577.13557520930226</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -15356,7 +15356,7 @@
       </c>
       <c r="I35" s="40">
         <f>D148*E148+D149*E149+D150*E150</f>
-        <v>538.78186046511621</v>
+        <v>569.57917446511624</v>
       </c>
       <c r="J35" s="21" t="s">
         <v>190</v>
@@ -15374,7 +15374,7 @@
       </c>
       <c r="D36" s="40">
         <f>bakimrecete!H61</f>
-        <v>203.82581395348836</v>
+        <v>224.73826095348835</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="I36" s="40">
         <f>D172*E172+D173*E173+D174*E174</f>
-        <v>1107.0934883720929</v>
+        <v>1175.608322372093</v>
       </c>
       <c r="J36" s="21" t="s">
         <v>190</v>
@@ -15399,7 +15399,7 @@
       </c>
       <c r="D37" s="40">
         <f>bakimrecete!H68</f>
-        <v>203.82581395348836</v>
+        <v>224.73826095348835</v>
       </c>
       <c r="E37">
         <v>6</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="I37" s="40">
         <f>D196*E196+D197*E197+D198+E198</f>
-        <v>1156.6104651162791</v>
+        <v>1205.315610116279</v>
       </c>
       <c r="J37" s="21" t="s">
         <v>190</v>
@@ -15424,7 +15424,7 @@
       </c>
       <c r="D38" s="40">
         <f>bakimrecete!H76</f>
-        <v>212.58697674418602</v>
+        <v>276.73872474418602</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="I38" s="40">
         <f>D127*E127+D128*E128+D129*E129</f>
-        <v>427.68269767441859</v>
+        <v>441.8507406744186</v>
       </c>
       <c r="J38" s="21" t="s">
         <v>192</v>
@@ -15449,7 +15449,7 @@
       </c>
       <c r="D39" s="40">
         <f>bakimrecete!H90</f>
-        <v>391.86465116279066</v>
+        <v>496.87438216279065</v>
       </c>
       <c r="E39">
         <v>2</v>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="I39" s="40">
         <f>D151*E151+D152*E152+D153*E153</f>
-        <v>575.16037209302317</v>
+        <v>593.1481130930232</v>
       </c>
       <c r="J39" s="21" t="s">
         <v>192</v>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="D40" s="40">
         <f>bakimrecete!H105</f>
-        <v>494.12883720930233</v>
+        <v>599.13856820930232</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="I40" s="40">
         <f>D175*E175+D176*E176+D177*E177</f>
-        <v>1201.1053023255813</v>
+        <v>1239.7897333255814</v>
       </c>
       <c r="J40" s="21" t="s">
         <v>192</v>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="D41" s="40">
         <f>bakimrecete!H112</f>
-        <v>281.69860465116278</v>
+        <v>290.23299265116282</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="I41" s="40">
         <f>D157*E157+D158*E158+D159*E159</f>
-        <v>644.19037209302314</v>
+        <v>717.33998609302319</v>
       </c>
       <c r="J41" s="21" t="s">
         <v>192</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="D42" s="40">
         <f>bakimrecete!H119</f>
-        <v>281.69860465116278</v>
+        <v>290.23299265116282</v>
       </c>
       <c r="E42">
         <v>6</v>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="I42" s="40">
         <f>D130*E130+D131*E131+D132*E132</f>
-        <v>453.38269767441852</v>
+        <v>488.08761067441856</v>
       </c>
       <c r="J42" s="21" t="s">
         <v>194</v>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="D43" s="40">
         <f>bakimrecete!H129</f>
-        <v>213.43860465116279</v>
+        <v>274.82546665116274</v>
       </c>
       <c r="E43">
         <v>3</v>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="I43" s="40">
         <f>D154*E154+D155*E155+D156*E156</f>
-        <v>581.35037209302322</v>
+        <v>604.28454209302322</v>
       </c>
       <c r="J43" s="21" t="s">
         <v>194</v>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="D44" s="40">
         <f>bakimrecete!H146</f>
-        <v>556.81744186046512</v>
+        <v>719.03474186046503</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="I44" s="40">
         <f>D178*E178+D179*E179+D180*E180</f>
-        <v>1208.9153023255813</v>
+        <v>1253.8407043255813</v>
       </c>
       <c r="J44" s="21" t="s">
         <v>194</v>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="D45" s="40">
         <f>bakimrecete!H164</f>
-        <v>761.34581395348835</v>
+        <v>923.56311395348825</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -15611,7 +15611,7 @@
       </c>
       <c r="I45" s="40">
         <f>D202*E202+D203*E203+D204*E204</f>
-        <v>1874.8984651162789</v>
+        <v>1948.7273141162789</v>
       </c>
       <c r="J45" s="21" t="s">
         <v>194</v>
@@ -15629,17 +15629,17 @@
       </c>
       <c r="D46" s="40">
         <f>bakimrecete!H171</f>
-        <v>253.67046511627908</v>
+        <v>257.25842411627906</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
-      <c r="H46" s="59" t="s">
+      <c r="H46" s="56" t="s">
         <v>482</v>
       </c>
       <c r="I46" s="40">
         <f>D130*E130+D131*E131+D132*E132</f>
-        <v>453.38269767441852</v>
+        <v>488.08761067441856</v>
       </c>
       <c r="J46" s="21" t="s">
         <v>193</v>
@@ -15653,17 +15653,17 @@
       </c>
       <c r="D47" s="40">
         <f>bakimrecete!H188</f>
-        <v>213.43860465116279</v>
+        <v>274.82546665116274</v>
       </c>
       <c r="E47">
         <v>6</v>
       </c>
-      <c r="H47" s="59" t="s">
+      <c r="H47" s="56" t="s">
         <v>483</v>
       </c>
       <c r="I47" s="40">
         <f>D154*E154+D155*E155+D156*E156</f>
-        <v>581.35037209302322</v>
+        <v>604.28454209302322</v>
       </c>
       <c r="J47" s="21" t="s">
         <v>193</v>
@@ -15677,17 +15677,17 @@
       </c>
       <c r="D48" s="40">
         <f>bakimrecete!H188</f>
-        <v>213.43860465116279</v>
+        <v>274.82546665116274</v>
       </c>
       <c r="E48">
         <v>3</v>
       </c>
-      <c r="H48" s="59" t="s">
+      <c r="H48" s="56" t="s">
         <v>484</v>
       </c>
       <c r="I48" s="40">
         <f>D178*E178+D179*E179+D180*E180</f>
-        <v>1208.9153023255813</v>
+        <v>1253.8407043255813</v>
       </c>
       <c r="J48" s="21" t="s">
         <v>193</v>
@@ -15701,17 +15701,17 @@
       </c>
       <c r="D49" s="40">
         <f>bakimrecete!H204</f>
-        <v>470.13930232558135</v>
+        <v>580.54295832558137</v>
       </c>
       <c r="E49">
         <v>2</v>
       </c>
-      <c r="H49" s="59" t="s">
+      <c r="H49" s="56" t="s">
         <v>485</v>
       </c>
       <c r="I49" s="40">
         <f>D202*E202+D203*E203+D204*E204</f>
-        <v>1874.8984651162789</v>
+        <v>1948.7273141162789</v>
       </c>
       <c r="J49" s="21" t="s">
         <v>193</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="D50" s="40">
         <f>bakimrecete!H222</f>
-        <v>878.77465116279063</v>
+        <v>1046.9052911627907</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="I50" s="40">
         <f>D133*E133+D134*E134+D135*E135</f>
-        <v>473.70269767441857</v>
+        <v>524.64532267441859</v>
       </c>
       <c r="J50" s="21" t="s">
         <v>196</v>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="D51" s="40">
         <f>bakimrecete!H229</f>
-        <v>302.38395348837207</v>
+        <v>327.11609848837213</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -15764,7 +15764,7 @@
       </c>
       <c r="I51" s="40">
         <f>D157*E157+D158*E158+D159*E159</f>
-        <v>644.19037209302314</v>
+        <v>717.33998609302319</v>
       </c>
       <c r="J51" s="21" t="s">
         <v>196</v>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="D52" s="40">
         <f>bakimrecete!H235</f>
-        <v>124.13953488372093</v>
+        <v>176.88013488372093</v>
       </c>
       <c r="E52">
         <v>6</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="I52" s="40">
         <f>D181*E181+D182*E182+D183*E183</f>
-        <v>1316.1553023255813</v>
+        <v>1446.7761883255812</v>
       </c>
       <c r="J52" s="21" t="s">
         <v>196</v>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="D53" s="40">
         <f>bakimrecete!H247</f>
-        <v>328.34162790697673</v>
+        <v>470.44558090697677</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="I53" s="40">
         <f>D205*E205+D206*E206+D207*E207</f>
-        <v>2065.2984651162787</v>
+        <v>2291.2759541162786</v>
       </c>
       <c r="J53" s="21" t="s">
         <v>196</v>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="D54" s="40">
         <f>bakimrecete!H265</f>
-        <v>665.77720930232556</v>
+        <v>858.61602130232563</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -15836,7 +15836,7 @@
       </c>
       <c r="I54" s="40">
         <f>D136*E136+D137*E137+D138*E138</f>
-        <v>493.86</v>
+        <v>519.47914600000001</v>
       </c>
       <c r="J54" s="21" t="s">
         <v>197</v>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="D55" s="40">
         <f>bakimrecete!H285</f>
-        <v>1074.4125581395347</v>
+        <v>1324.978354139535</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="I55" s="40">
         <f>D160*E160+D161*E161+D162*E162</f>
-        <v>652.78302325581399</v>
+        <v>685.45822225581401</v>
       </c>
       <c r="J55" s="21" t="s">
         <v>197</v>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="D56" s="40">
         <f>bakimrecete!H292</f>
-        <v>308.64837209302323</v>
+        <v>320.74674609302326</v>
       </c>
       <c r="E56" s="9">
         <v>1</v>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="I56" s="40">
         <f>D184*E184+D185*E185+D186*E186</f>
-        <v>1391.8895348837211</v>
+        <v>1461.6909198837211</v>
       </c>
       <c r="J56" s="21" t="s">
         <v>197</v>
@@ -15902,7 +15902,7 @@
       </c>
       <c r="D57" s="40">
         <f>bakimrecete!H301</f>
-        <v>406.81116279069772</v>
+        <v>603.19797879069768</v>
       </c>
       <c r="E57" s="35">
         <v>3</v>
@@ -15912,7 +15912,7 @@
       </c>
       <c r="I57" s="40">
         <f>D208*E208+D209*E209+D210*E210</f>
-        <v>2134.3630232558139</v>
+        <v>2243.8956602558137</v>
       </c>
       <c r="J57" s="21" t="s">
         <v>197</v>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="D58" s="40">
         <f>bakimrecete!H321</f>
-        <v>857.97162790697678</v>
+        <v>1186.7533319069767</v>
       </c>
       <c r="E58" s="35">
         <v>2</v>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="I58" s="40">
         <f>D139*E139+D140*E140+D141*E141</f>
-        <v>592.77674418604659</v>
+        <v>685.85591218604645</v>
       </c>
       <c r="J58" s="21" t="s">
         <v>427</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="D59" s="40">
         <f>bakimrecete!H345</f>
-        <v>1445.1504651162791</v>
+        <v>1875.4098781162793</v>
       </c>
       <c r="E59" s="35">
         <v>1</v>
@@ -15960,7 +15960,7 @@
       </c>
       <c r="I59" s="40">
         <f>D154*E154+D155*E155+D156*E156</f>
-        <v>581.35037209302322</v>
+        <v>604.28454209302322</v>
       </c>
       <c r="J59" s="21" t="s">
         <v>427</v>
@@ -15978,7 +15978,7 @@
       </c>
       <c r="D60" s="40">
         <f>bakimrecete!H8</f>
-        <v>188.33581395348835</v>
+        <v>196.87020195348836</v>
       </c>
       <c r="E60" s="35">
         <v>1</v>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="I60" s="40">
         <f>D187*E187+D188*E188+D189*E189</f>
-        <v>1627.532093023256</v>
+        <v>1860.2300130232557</v>
       </c>
       <c r="J60" s="21" t="s">
         <v>427</v>
@@ -16002,7 +16002,7 @@
       </c>
       <c r="D61" s="40">
         <f>bakimrecete!H15</f>
-        <v>188.33581395348835</v>
+        <v>196.87020195348836</v>
       </c>
       <c r="E61" s="35">
         <v>12</v>
@@ -16012,7 +16012,7 @@
       </c>
       <c r="I61" s="40">
         <f>D211*E211+D212*E212+D213*E213</f>
-        <v>2602.8353488372095</v>
+        <v>3021.6916048372095</v>
       </c>
       <c r="J61" s="21" t="s">
         <v>427</v>
@@ -16026,7 +16026,7 @@
       </c>
       <c r="D62" s="40">
         <f>bakimrecete!H23</f>
-        <v>184.66697674418603</v>
+        <v>226.50785274418604</v>
       </c>
       <c r="E62" s="35">
         <v>6</v>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="D63" s="40">
         <f>bakimrecete!H38</f>
-        <v>379.6346511627907</v>
+        <v>474.87138916279071</v>
       </c>
       <c r="E63" s="35">
         <v>3</v>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="D64" s="40">
         <f>bakimrecete!H54</f>
-        <v>481.89883720930231</v>
+        <v>577.13557520930226</v>
       </c>
       <c r="E64" s="35">
         <v>3</v>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="D65" s="40">
         <f>bakimrecete!H61</f>
-        <v>203.82581395348836</v>
+        <v>224.73826095348835</v>
       </c>
       <c r="E65" s="35">
         <v>1</v>
@@ -16088,7 +16088,7 @@
       </c>
       <c r="D66" s="40">
         <f>bakimrecete!H68</f>
-        <v>203.82581395348836</v>
+        <v>224.73826095348835</v>
       </c>
       <c r="E66" s="35">
         <v>12</v>
@@ -16103,7 +16103,7 @@
       </c>
       <c r="D67" s="40">
         <f>bakimrecete!H76</f>
-        <v>212.58697674418602</v>
+        <v>276.73872474418602</v>
       </c>
       <c r="E67" s="35">
         <v>6</v>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="D68" s="40">
         <f>bakimrecete!H90</f>
-        <v>391.86465116279066</v>
+        <v>496.87438216279065</v>
       </c>
       <c r="E68" s="35">
         <v>3</v>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="D69" s="40">
         <f>bakimrecete!H105</f>
-        <v>494.12883720930233</v>
+        <v>599.13856820930232</v>
       </c>
       <c r="E69" s="35">
         <v>3</v>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="D70" s="40">
         <f>bakimrecete!H112</f>
-        <v>281.69860465116278</v>
+        <v>290.23299265116282</v>
       </c>
       <c r="E70" s="35">
         <v>1</v>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="D71" s="40">
         <f>bakimrecete!H119</f>
-        <v>281.69860465116278</v>
+        <v>290.23299265116282</v>
       </c>
       <c r="E71" s="35">
         <v>12</v>
@@ -16181,7 +16181,7 @@
       </c>
       <c r="D72" s="40">
         <f>bakimrecete!H129</f>
-        <v>213.43860465116279</v>
+        <v>274.82546665116274</v>
       </c>
       <c r="E72" s="35">
         <v>6</v>
@@ -16196,7 +16196,7 @@
       </c>
       <c r="D73" s="40">
         <f>bakimrecete!H146</f>
-        <v>556.81744186046512</v>
+        <v>719.03474186046503</v>
       </c>
       <c r="E73" s="35">
         <v>3</v>
@@ -16211,7 +16211,7 @@
       </c>
       <c r="D74" s="40">
         <f>bakimrecete!H164</f>
-        <v>761.34581395348835</v>
+        <v>923.56311395348825</v>
       </c>
       <c r="E74" s="35">
         <v>3</v>
@@ -16229,7 +16229,7 @@
       </c>
       <c r="D75" s="40">
         <f>bakimrecete!H171</f>
-        <v>253.67046511627908</v>
+        <v>257.25842411627906</v>
       </c>
       <c r="E75" s="35">
         <v>1</v>
@@ -16244,7 +16244,7 @@
       </c>
       <c r="D76" s="40">
         <f>bakimrecete!H178</f>
-        <v>253.67046511627908</v>
+        <v>257.25842411627906</v>
       </c>
       <c r="E76" s="35">
         <v>12</v>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="D77" s="40">
         <f>bakimrecete!H188</f>
-        <v>213.43860465116279</v>
+        <v>274.82546665116274</v>
       </c>
       <c r="E77" s="35">
         <v>6</v>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="D78" s="40">
         <f>bakimrecete!H204</f>
-        <v>470.13930232558135</v>
+        <v>580.54295832558137</v>
       </c>
       <c r="E78" s="35">
         <v>3</v>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="D79" s="40">
         <f>bakimrecete!H222</f>
-        <v>878.77465116279063</v>
+        <v>1046.9052911627907</v>
       </c>
       <c r="E79" s="35">
         <v>3</v>
@@ -16307,7 +16307,7 @@
       </c>
       <c r="D80" s="40">
         <f>bakimrecete!H229</f>
-        <v>302.38395348837207</v>
+        <v>327.11609848837213</v>
       </c>
       <c r="E80" s="35">
         <v>1</v>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="D81" s="40">
         <f>bakimrecete!H235</f>
-        <v>124.13953488372093</v>
+        <v>176.88013488372093</v>
       </c>
       <c r="E81" s="35">
         <v>12</v>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="D82" s="40">
         <f>bakimrecete!H247</f>
-        <v>328.34162790697673</v>
+        <v>470.44558090697677</v>
       </c>
       <c r="E82" s="35">
         <v>6</v>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="D83" s="40">
         <f>bakimrecete!H265</f>
-        <v>665.77720930232556</v>
+        <v>858.61602130232563</v>
       </c>
       <c r="E83" s="35">
         <v>3</v>
@@ -16367,7 +16367,7 @@
       </c>
       <c r="D84" s="40">
         <f>bakimrecete!H285</f>
-        <v>1074.4125581395347</v>
+        <v>1324.978354139535</v>
       </c>
       <c r="E84" s="35">
         <v>3</v>
@@ -16385,7 +16385,7 @@
       </c>
       <c r="D85" s="40">
         <f>bakimrecete!H292</f>
-        <v>308.64837209302323</v>
+        <v>320.74674609302326</v>
       </c>
       <c r="E85" s="35">
         <v>1</v>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="D86" s="40">
         <f>bakimrecete!H301</f>
-        <v>406.81116279069772</v>
+        <v>603.19797879069768</v>
       </c>
       <c r="E86" s="35">
         <v>6</v>
@@ -16415,7 +16415,7 @@
       </c>
       <c r="D87" s="40">
         <f>bakimrecete!H321</f>
-        <v>857.97162790697678</v>
+        <v>1186.7533319069767</v>
       </c>
       <c r="E87" s="35">
         <v>2</v>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="D88" s="40">
         <f>bakimrecete!H345</f>
-        <v>1445.1504651162791</v>
+        <v>1875.4098781162793</v>
       </c>
       <c r="E88" s="35">
         <v>3</v>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="D89" s="40">
         <f>bakimrecete!H8</f>
-        <v>188.33581395348835</v>
+        <v>196.87020195348836</v>
       </c>
       <c r="E89" s="35">
         <v>1</v>
@@ -16463,7 +16463,7 @@
       </c>
       <c r="D90" s="40">
         <f>bakimrecete!H15</f>
-        <v>188.33581395348835</v>
+        <v>196.87020195348836</v>
       </c>
       <c r="E90" s="35">
         <v>18</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="D91" s="40">
         <f>bakimrecete!H23</f>
-        <v>184.66697674418603</v>
+        <v>226.50785274418604</v>
       </c>
       <c r="E91" s="35">
         <v>9</v>
@@ -16493,7 +16493,7 @@
       </c>
       <c r="D92" s="40">
         <f>bakimrecete!H38</f>
-        <v>379.6346511627907</v>
+        <v>474.87138916279071</v>
       </c>
       <c r="E92" s="35">
         <v>5</v>
@@ -16508,7 +16508,7 @@
       </c>
       <c r="D93" s="40">
         <f>bakimrecete!H54</f>
-        <v>481.89883720930231</v>
+        <v>577.13557520930226</v>
       </c>
       <c r="E93" s="35">
         <v>4</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="D94" s="40">
         <f>bakimrecete!H61</f>
-        <v>203.82581395348836</v>
+        <v>224.73826095348835</v>
       </c>
       <c r="E94" s="35">
         <v>1</v>
@@ -16540,7 +16540,7 @@
       </c>
       <c r="D95" s="40">
         <f>bakimrecete!H68</f>
-        <v>203.82581395348836</v>
+        <v>224.73826095348835</v>
       </c>
       <c r="E95" s="35">
         <v>18</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="D96" s="40">
         <f>bakimrecete!H76</f>
-        <v>212.58697674418602</v>
+        <v>276.73872474418602</v>
       </c>
       <c r="E96" s="35">
         <v>9</v>
@@ -16568,7 +16568,7 @@
       </c>
       <c r="D97" s="40">
         <f>bakimrecete!H90</f>
-        <v>391.86465116279066</v>
+        <v>496.87438216279065</v>
       </c>
       <c r="E97" s="35">
         <v>5</v>
@@ -16582,7 +16582,7 @@
       </c>
       <c r="D98" s="40">
         <f>bakimrecete!H105</f>
-        <v>494.12883720930233</v>
+        <v>599.13856820930232</v>
       </c>
       <c r="E98" s="35">
         <v>4</v>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="D99" s="40">
         <f>bakimrecete!H112</f>
-        <v>281.69860465116278</v>
+        <v>290.23299265116282</v>
       </c>
       <c r="E99" s="35">
         <v>1</v>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="D100" s="40">
         <f>bakimrecete!H119</f>
-        <v>281.69860465116278</v>
+        <v>290.23299265116282</v>
       </c>
       <c r="E100" s="35">
         <v>18</v>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="D101" s="40">
         <f>bakimrecete!H129</f>
-        <v>213.43860465116279</v>
+        <v>274.82546665116274</v>
       </c>
       <c r="E101" s="35">
         <v>9</v>
@@ -16642,7 +16642,7 @@
       </c>
       <c r="D102" s="40">
         <f>bakimrecete!H146</f>
-        <v>556.81744186046512</v>
+        <v>719.03474186046503</v>
       </c>
       <c r="E102" s="35">
         <v>5</v>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="D103" s="40">
         <f>bakimrecete!H164</f>
-        <v>761.34581395348835</v>
+        <v>923.56311395348825</v>
       </c>
       <c r="E103" s="35">
         <v>4</v>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="D104" s="40">
         <f>bakimrecete!H171</f>
-        <v>253.67046511627908</v>
+        <v>257.25842411627906</v>
       </c>
       <c r="E104" s="35">
         <v>1</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="D105" s="40">
         <f>bakimrecete!H178</f>
-        <v>253.67046511627908</v>
+        <v>257.25842411627906</v>
       </c>
       <c r="E105" s="35">
         <v>18</v>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="D106" s="40">
         <f>bakimrecete!H188</f>
-        <v>213.43860465116279</v>
+        <v>274.82546665116274</v>
       </c>
       <c r="E106" s="35">
         <v>9</v>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="D107" s="40">
         <f>bakimrecete!H204</f>
-        <v>470.13930232558135</v>
+        <v>580.54295832558137</v>
       </c>
       <c r="E107" s="35">
         <v>5</v>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="D108" s="40">
         <f>bakimrecete!H222</f>
-        <v>878.77465116279063</v>
+        <v>1046.9052911627907</v>
       </c>
       <c r="E108" s="35">
         <v>4</v>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="D109" s="40">
         <f>bakimrecete!H229</f>
-        <v>302.38395348837207</v>
+        <v>327.11609848837213</v>
       </c>
       <c r="E109" s="35">
         <v>1</v>
@@ -16762,7 +16762,7 @@
       </c>
       <c r="D110" s="40">
         <f>bakimrecete!H235</f>
-        <v>124.13953488372093</v>
+        <v>176.88013488372093</v>
       </c>
       <c r="E110" s="35">
         <v>18</v>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="D111" s="40">
         <f>bakimrecete!H247</f>
-        <v>328.34162790697673</v>
+        <v>470.44558090697677</v>
       </c>
       <c r="E111" s="35">
         <v>9</v>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="D112" s="40">
         <f>bakimrecete!H265</f>
-        <v>665.77720930232556</v>
+        <v>858.61602130232563</v>
       </c>
       <c r="E112" s="35">
         <v>5</v>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="D113" s="40">
         <f>bakimrecete!H285</f>
-        <v>1074.4125581395347</v>
+        <v>1324.978354139535</v>
       </c>
       <c r="E113" s="35">
         <v>4</v>
@@ -16822,7 +16822,7 @@
       </c>
       <c r="D114" s="40">
         <f>bakimrecete!H292</f>
-        <v>308.64837209302323</v>
+        <v>320.74674609302326</v>
       </c>
       <c r="E114" s="35">
         <v>1</v>
@@ -16836,7 +16836,7 @@
       </c>
       <c r="D115" s="40">
         <f>bakimrecete!H301</f>
-        <v>406.81116279069772</v>
+        <v>603.19797879069768</v>
       </c>
       <c r="E115" s="35">
         <v>9</v>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="D116" s="40">
         <f>bakimrecete!H321</f>
-        <v>857.97162790697678</v>
+        <v>1186.7533319069767</v>
       </c>
       <c r="E116" s="35">
         <v>5</v>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="D117" s="40">
         <f>bakimrecete!H345</f>
-        <v>1445.1504651162791</v>
+        <v>1875.4098781162793</v>
       </c>
       <c r="E117" s="35">
         <v>4</v>
@@ -16896,7 +16896,7 @@
       </c>
       <c r="D119" s="41">
         <f>bakimrecete!H352</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
       <c r="E119" s="35">
         <v>1</v>
@@ -16910,7 +16910,7 @@
       </c>
       <c r="D120" s="41">
         <f>bakimrecete!H360</f>
-        <v>187.17558139534884</v>
+        <v>206.0343413953488</v>
       </c>
       <c r="E120" s="35">
         <v>1</v>
@@ -16942,7 +16942,7 @@
       </c>
       <c r="D122" s="41">
         <f>bakimrecete!H367</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
       <c r="E122" s="35">
         <v>1</v>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="D123" s="41">
         <f>bakimrecete!H375</f>
-        <v>187.17558139534884</v>
+        <v>206.0343413953488</v>
       </c>
       <c r="E123" s="35">
         <v>1</v>
@@ -16988,7 +16988,7 @@
       </c>
       <c r="D125" s="41">
         <f>bakimrecete!H382</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
       <c r="E125" s="35">
         <v>1</v>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="D126" s="41">
         <f>bakimrecete!H390</f>
-        <v>191.39999999999998</v>
+        <v>210.25876</v>
       </c>
       <c r="E126" s="35">
         <v>1</v>
@@ -17034,7 +17034,7 @@
       </c>
       <c r="D128" s="41">
         <f>bakimrecete!H397</f>
-        <v>81.942790697674411</v>
+        <v>85.762488697674414</v>
       </c>
       <c r="E128" s="35">
         <v>1</v>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="D129" s="41">
         <f>bakimrecete!H405</f>
-        <v>214.6701395348837</v>
+        <v>225.0184845348837</v>
       </c>
       <c r="E129" s="35">
         <v>1</v>
@@ -17080,7 +17080,7 @@
       </c>
       <c r="D131" s="41">
         <f>bakimrecete!H412</f>
-        <v>84.632790697674409</v>
+        <v>90.602067697674414</v>
       </c>
       <c r="E131" s="35">
         <v>1</v>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="D132" s="41">
         <f>bakimrecete!H448</f>
-        <v>237.68013953488369</v>
+        <v>266.41577553488366</v>
       </c>
       <c r="E132" s="35">
         <v>1</v>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="D134" s="41">
         <f>bakimrecete!H440</f>
-        <v>104.95279069767442</v>
+        <v>127.15977969767442</v>
       </c>
       <c r="E134" s="35">
         <v>1</v>
@@ -17140,7 +17140,7 @@
       </c>
       <c r="D135" s="41">
         <f>bakimrecete!H448</f>
-        <v>237.68013953488369</v>
+        <v>266.41577553488366</v>
       </c>
       <c r="E135" s="35">
         <v>1</v>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="D137" s="41">
         <f>bakimrecete!H455</f>
-        <v>89.690465116279057</v>
+        <v>96.746518116279063</v>
       </c>
       <c r="E137" s="35">
         <v>1</v>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="D138" s="41">
         <f>bakimrecete!H463</f>
-        <v>265.70441860465121</v>
+        <v>284.26751160465119</v>
       </c>
       <c r="E138" s="35">
         <v>1</v>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="D140" s="41">
         <f>bakimrecete!H472</f>
-        <v>150.79813953488372</v>
+        <v>197.33772353488371</v>
       </c>
       <c r="E140" s="35">
         <v>1</v>
@@ -17232,7 +17232,7 @@
       </c>
       <c r="D141" s="41">
         <f>bakimrecete!H480</f>
-        <v>280.11813953488377</v>
+        <v>326.6577235348837</v>
       </c>
       <c r="E141" s="35">
         <v>1</v>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="D143" s="41">
         <f>bakimrecete!H352</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
       <c r="E143" s="35">
         <v>2</v>
@@ -17278,7 +17278,7 @@
       </c>
       <c r="D144" s="41">
         <f>bakimrecete!H360</f>
-        <v>187.17558139534884</v>
+        <v>206.0343413953488</v>
       </c>
       <c r="E144" s="35">
         <v>1</v>
@@ -17310,7 +17310,7 @@
       </c>
       <c r="D146" s="41">
         <f>bakimrecete!H367</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
       <c r="E146">
         <v>2</v>
@@ -17324,7 +17324,7 @@
       </c>
       <c r="D147" s="41">
         <f>bakimrecete!H375</f>
-        <v>187.17558139534884</v>
+        <v>206.0343413953488</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="D149" s="41">
         <f>bakimrecete!H382</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
       <c r="E149">
         <v>2</v>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="D150" s="41">
         <f>bakimrecete!H390</f>
-        <v>191.39999999999998</v>
+        <v>210.25876</v>
       </c>
       <c r="E150">
         <v>1</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="D152" s="41">
         <f>bakimrecete!H397</f>
-        <v>81.942790697674411</v>
+        <v>85.762488697674414</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -17418,7 +17418,7 @@
       </c>
       <c r="D153" s="41">
         <f>bakimrecete!H405</f>
-        <v>214.6701395348837</v>
+        <v>225.0184845348837</v>
       </c>
       <c r="E153">
         <v>1</v>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="D155" s="41">
         <f>bakimrecete!H412</f>
-        <v>84.632790697674409</v>
+        <v>90.602067697674414</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="D156" s="41">
         <f>bakimrecete!H419</f>
-        <v>215.4801395348837</v>
+        <v>226.47575553488372</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -17496,7 +17496,7 @@
       </c>
       <c r="D158" s="41">
         <f>bakimrecete!H440</f>
-        <v>104.95279069767442</v>
+        <v>127.15977969767442</v>
       </c>
       <c r="E158">
         <v>2</v>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="D159" s="41">
         <f>bakimrecete!H448</f>
-        <v>237.68013953488369</v>
+        <v>266.41577553488366</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="D161" s="41">
         <f>bakimrecete!H455</f>
-        <v>89.690465116279057</v>
+        <v>96.746518116279063</v>
       </c>
       <c r="E161">
         <v>2</v>
@@ -17556,7 +17556,7 @@
       </c>
       <c r="D162" s="41">
         <f>bakimrecete!H463</f>
-        <v>265.70441860465121</v>
+        <v>284.26751160465119</v>
       </c>
       <c r="E162">
         <v>1</v>
@@ -17588,7 +17588,7 @@
       </c>
       <c r="D164" s="41">
         <f>bakimrecete!H472</f>
-        <v>150.79813953488372</v>
+        <v>197.33772353488371</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -17602,7 +17602,7 @@
       </c>
       <c r="D165" s="41">
         <f>bakimrecete!H480</f>
-        <v>280.11813953488377</v>
+        <v>326.6577235348837</v>
       </c>
       <c r="E165">
         <v>1</v>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="D167" s="42">
         <f>bakimrecete!H352</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
       <c r="E167">
         <v>2</v>
@@ -17648,7 +17648,7 @@
       </c>
       <c r="D168" s="42">
         <f>bakimrecete!H360</f>
-        <v>187.17558139534884</v>
+        <v>206.0343413953488</v>
       </c>
       <c r="E168">
         <v>3</v>
@@ -17680,7 +17680,7 @@
       </c>
       <c r="D170" s="42">
         <f>bakimrecete!H367</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
       <c r="E170">
         <v>2</v>
@@ -17694,7 +17694,7 @@
       </c>
       <c r="D171" s="42">
         <f>bakimrecete!H375</f>
-        <v>187.17558139534884</v>
+        <v>206.0343413953488</v>
       </c>
       <c r="E171">
         <v>3</v>
@@ -17726,7 +17726,7 @@
       </c>
       <c r="D173" s="42">
         <f>bakimrecete!H382</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
       <c r="E173">
         <v>2</v>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="D174" s="42">
         <f>bakimrecete!H390</f>
-        <v>191.39999999999998</v>
+        <v>210.25876</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="D176" s="42">
         <f>bakimrecete!H397</f>
-        <v>81.942790697674411</v>
+        <v>85.762488697674414</v>
       </c>
       <c r="E176">
         <v>2</v>
@@ -17786,7 +17786,7 @@
       </c>
       <c r="D177" s="42">
         <f>bakimrecete!H405</f>
-        <v>214.6701395348837</v>
+        <v>225.0184845348837</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -17818,7 +17818,7 @@
       </c>
       <c r="D179" s="42">
         <f>bakimrecete!H412</f>
-        <v>84.632790697674409</v>
+        <v>90.602067697674414</v>
       </c>
       <c r="E179">
         <v>2</v>
@@ -17832,7 +17832,7 @@
       </c>
       <c r="D180" s="42">
         <f>bakimrecete!H419</f>
-        <v>215.4801395348837</v>
+        <v>226.47575553488372</v>
       </c>
       <c r="E180">
         <v>3</v>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="D182" s="42">
         <f>bakimrecete!H440</f>
-        <v>104.95279069767442</v>
+        <v>127.15977969767442</v>
       </c>
       <c r="E182">
         <v>2</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="D183" s="42">
         <f>bakimrecete!H448</f>
-        <v>237.68013953488369</v>
+        <v>266.41577553488366</v>
       </c>
       <c r="E183">
         <v>3</v>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="D185" s="42">
         <f>bakimrecete!H455</f>
-        <v>89.690465116279057</v>
+        <v>96.746518116279063</v>
       </c>
       <c r="E185">
         <v>2</v>
@@ -17924,7 +17924,7 @@
       </c>
       <c r="D186" s="42">
         <f>bakimrecete!H463</f>
-        <v>265.70441860465121</v>
+        <v>284.26751160465119</v>
       </c>
       <c r="E186">
         <v>3</v>
@@ -17956,7 +17956,7 @@
       </c>
       <c r="D188" s="42">
         <f>bakimrecete!H472</f>
-        <v>150.79813953488372</v>
+        <v>197.33772353488371</v>
       </c>
       <c r="E188">
         <v>2</v>
@@ -17970,7 +17970,7 @@
       </c>
       <c r="D189" s="42">
         <f>bakimrecete!H480</f>
-        <v>280.11813953488377</v>
+        <v>326.6577235348837</v>
       </c>
       <c r="E189">
         <v>3</v>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="D191" s="41">
         <f>bakimrecete!H352</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
       <c r="E191">
         <v>5</v>
@@ -18016,7 +18016,7 @@
       </c>
       <c r="D192" s="41">
         <f>bakimrecete!H360</f>
-        <v>187.17558139534884</v>
+        <v>206.0343413953488</v>
       </c>
       <c r="E192">
         <v>4</v>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="D194" s="41">
         <f>bakimrecete!H367</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
       <c r="E194">
         <v>5</v>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="D195" s="41">
         <f>bakimrecete!H375</f>
-        <v>187.17558139534884</v>
+        <v>206.0343413953488</v>
       </c>
       <c r="E195">
         <v>4</v>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="D197" s="41">
         <f>bakimrecete!H382</f>
-        <v>80.93511627906976</v>
+        <v>86.904393279069765</v>
       </c>
       <c r="E197">
         <v>5</v>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="D198" s="41">
         <f>bakimrecete!H390</f>
-        <v>191.39999999999998</v>
+        <v>210.25876</v>
       </c>
       <c r="E198">
         <v>4</v>
@@ -18140,7 +18140,7 @@
       </c>
       <c r="D200" s="41">
         <f>bakimrecete!H412</f>
-        <v>84.632790697674409</v>
+        <v>90.602067697674414</v>
       </c>
       <c r="E200">
         <v>5</v>
@@ -18154,7 +18154,7 @@
       </c>
       <c r="D201" s="41">
         <f>bakimrecete!H419</f>
-        <v>215.4801395348837</v>
+        <v>226.47575553488372</v>
       </c>
       <c r="E201">
         <v>4</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="D203" s="41">
         <f>bakimrecete!H412</f>
-        <v>84.632790697674409</v>
+        <v>90.602067697674414</v>
       </c>
       <c r="E203">
         <v>5</v>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="D204" s="41">
         <f>bakimrecete!H419</f>
-        <v>215.4801395348837</v>
+        <v>226.47575553488372</v>
       </c>
       <c r="E204">
         <v>4</v>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="D206" s="41">
         <f>bakimrecete!H440</f>
-        <v>104.95279069767442</v>
+        <v>127.15977969767442</v>
       </c>
       <c r="E206">
         <v>5</v>
@@ -18246,7 +18246,7 @@
       </c>
       <c r="D207" s="41">
         <f>bakimrecete!H448</f>
-        <v>237.68013953488369</v>
+        <v>266.41577553488366</v>
       </c>
       <c r="E207">
         <v>4</v>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="D209" s="41">
         <f>bakimrecete!H455</f>
-        <v>89.690465116279057</v>
+        <v>96.746518116279063</v>
       </c>
       <c r="E209">
         <v>5</v>
@@ -18292,7 +18292,7 @@
       </c>
       <c r="D210" s="41">
         <f>bakimrecete!H463</f>
-        <v>265.70441860465121</v>
+        <v>284.26751160465119</v>
       </c>
       <c r="E210">
         <v>4</v>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="D212" s="41">
         <f>bakimrecete!H472</f>
-        <v>150.79813953488372</v>
+        <v>197.33772353488371</v>
       </c>
       <c r="E212">
         <v>5</v>
@@ -18334,7 +18334,7 @@
       </c>
       <c r="D213" s="41">
         <f>bakimrecete!H480</f>
-        <v>280.11813953488377</v>
+        <v>326.6577235348837</v>
       </c>
       <c r="E213">
         <v>4</v>
@@ -18673,7 +18673,7 @@
         <v>30</v>
       </c>
       <c r="C2" s="45">
-        <v>110.51</v>
+        <v>198.81854100000001</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>98</v>
@@ -18687,7 +18687,7 @@
         <v>116</v>
       </c>
       <c r="C3" s="45">
-        <v>14.89</v>
+        <v>26.788599000000001</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>98</v>
@@ -18701,7 +18701,7 @@
         <v>118</v>
       </c>
       <c r="C4" s="45">
-        <v>7.98</v>
+        <v>14.356818000000001</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>98</v>
@@ -18715,7 +18715,7 @@
         <v>32</v>
       </c>
       <c r="C5" s="45">
-        <v>3.26</v>
+        <v>5.8650659999999997</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>98</v>
@@ -18729,7 +18729,7 @@
         <v>34</v>
       </c>
       <c r="C6" s="45">
-        <v>16.309999999999999</v>
+        <v>29.343320999999996</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>98</v>
@@ -18743,7 +18743,7 @@
         <v>36</v>
       </c>
       <c r="C7" s="45">
-        <v>11.83</v>
+        <v>21.283352999999998</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>98</v>
@@ -18757,7 +18757,7 @@
         <v>37</v>
       </c>
       <c r="C8" s="45">
-        <v>12.13</v>
+        <v>21.823083</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>98</v>
@@ -18771,7 +18771,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="45">
-        <v>11.24</v>
+        <v>20.221883999999999</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>98</v>
@@ -18785,7 +18785,7 @@
         <v>34</v>
       </c>
       <c r="C10" s="45">
-        <v>27.49</v>
+        <v>49.457258999999993</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>98</v>
@@ -18799,7 +18799,7 @@
         <v>34</v>
       </c>
       <c r="C11" s="45">
-        <v>17.28</v>
+        <v>31.088448</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>98</v>
@@ -18813,7 +18813,7 @@
         <v>122</v>
       </c>
       <c r="C12" s="45">
-        <v>3.51</v>
+        <v>6.3148409999999995</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>98</v>
@@ -18827,7 +18827,7 @@
         <v>34</v>
       </c>
       <c r="C13" s="45">
-        <v>51.82</v>
+        <v>93.229361999999995</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>98</v>
@@ -18841,7 +18841,7 @@
         <v>37</v>
       </c>
       <c r="C14" s="45">
-        <v>21.28</v>
+        <v>38.284848000000004</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>98</v>
@@ -18855,7 +18855,7 @@
         <v>43</v>
       </c>
       <c r="C15" s="45">
-        <v>8.09</v>
+        <v>14.554718999999999</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>98</v>
@@ -18869,7 +18869,7 @@
         <v>45</v>
       </c>
       <c r="C16" s="45">
-        <v>30.78</v>
+        <v>55.376297999999998</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>98</v>
@@ -18883,7 +18883,7 @@
         <v>46</v>
       </c>
       <c r="C17" s="45">
-        <v>21.09</v>
+        <v>37.943019</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>98</v>
@@ -18897,7 +18897,7 @@
         <v>125</v>
       </c>
       <c r="C18" s="45">
-        <v>32.76</v>
+        <v>58.938515999999993</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>98</v>
@@ -18911,7 +18911,7 @@
         <v>47</v>
       </c>
       <c r="C19" s="45">
-        <v>13.37</v>
+        <v>24.053966999999997</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>98</v>
@@ -18925,7 +18925,7 @@
         <v>34</v>
       </c>
       <c r="C20" s="45">
-        <v>16.309999999999999</v>
+        <v>29.343320999999996</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>98</v>
@@ -18939,7 +18939,7 @@
         <v>49</v>
       </c>
       <c r="C21" s="45">
-        <v>4.97</v>
+        <v>8.9415269999999989</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>98</v>
@@ -18953,7 +18953,7 @@
         <v>46</v>
       </c>
       <c r="C22" s="45">
-        <v>41.69</v>
+        <v>75.004478999999989</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>98</v>
@@ -18967,7 +18967,7 @@
         <v>49</v>
       </c>
       <c r="C23" s="45">
-        <v>15.14</v>
+        <v>27.238374</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>98</v>
@@ -18981,7 +18981,7 @@
         <v>47</v>
       </c>
       <c r="C24" s="45">
-        <v>20</v>
+        <v>35.981999999999999</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>98</v>
@@ -18995,7 +18995,7 @@
         <v>46</v>
       </c>
       <c r="C25" s="45">
-        <v>21.81</v>
+        <v>39.238370999999994</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>98</v>
@@ -19009,7 +19009,7 @@
         <v>34</v>
       </c>
       <c r="C26" s="45">
-        <v>28.84</v>
+        <v>51.886043999999998</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>98</v>
@@ -19023,7 +19023,7 @@
         <v>37</v>
       </c>
       <c r="C27" s="45">
-        <v>18</v>
+        <v>32.383800000000001</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>98</v>
@@ -19037,7 +19037,7 @@
         <v>131</v>
       </c>
       <c r="C28" s="45">
-        <v>3.21</v>
+        <v>5.7751109999999999</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>98</v>
@@ -19051,7 +19051,7 @@
         <v>45</v>
       </c>
       <c r="C29" s="45">
-        <v>78.099999999999994</v>
+        <v>140.50970999999998</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>98</v>
@@ -19065,7 +19065,7 @@
         <v>56</v>
       </c>
       <c r="C30" s="45">
-        <v>8.7899999999999991</v>
+        <v>15.814088999999997</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>98</v>
@@ -19079,7 +19079,7 @@
         <v>132</v>
       </c>
       <c r="C31" s="45">
-        <v>15.16</v>
+        <v>27.274355999999997</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>98</v>
@@ -19093,7 +19093,7 @@
         <v>59</v>
       </c>
       <c r="C32" s="45">
-        <v>77.540000000000006</v>
+        <v>139.50221400000001</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>98</v>
@@ -19107,7 +19107,7 @@
         <v>59</v>
       </c>
       <c r="C33" s="45">
-        <v>34.08</v>
+        <v>61.313327999999991</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>98</v>
@@ -19121,7 +19121,7 @@
         <v>49</v>
       </c>
       <c r="C34" s="45">
-        <v>30.95</v>
+        <v>55.682144999999998</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>98</v>
@@ -19135,7 +19135,7 @@
         <v>62</v>
       </c>
       <c r="C35" s="45">
-        <v>43.14</v>
+        <v>77.613174000000001</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>98</v>
@@ -19149,7 +19149,7 @@
         <v>135</v>
       </c>
       <c r="C36" s="45">
-        <v>1.87</v>
+        <v>3.3643170000000002</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>98</v>
@@ -19163,7 +19163,7 @@
         <v>64</v>
       </c>
       <c r="C37" s="45">
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>98</v>
@@ -19177,7 +19177,7 @@
         <v>65</v>
       </c>
       <c r="C38" s="45">
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>98</v>
@@ -19191,7 +19191,7 @@
         <v>64</v>
       </c>
       <c r="C39" s="45">
-        <v>1.88</v>
+        <v>3.3823079999999996</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>98</v>
@@ -19205,7 +19205,7 @@
         <v>137</v>
       </c>
       <c r="C40" s="45">
-        <v>8.83</v>
+        <v>15.886052999999999</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>98</v>
@@ -19219,7 +19219,7 @@
         <v>139</v>
       </c>
       <c r="C41" s="45">
-        <v>38.71</v>
+        <v>69.643160999999992</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>98</v>
@@ -19233,7 +19233,7 @@
         <v>68</v>
       </c>
       <c r="C42" s="45">
-        <v>14.73</v>
+        <v>26.500743</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>98</v>
@@ -19247,7 +19247,7 @@
         <v>70</v>
       </c>
       <c r="C43" s="45">
-        <v>24.45</v>
+        <v>43.987994999999998</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>98</v>
@@ -19261,7 +19261,7 @@
         <v>68</v>
       </c>
       <c r="C44" s="45">
-        <v>6.7</v>
+        <v>12.05397</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>98</v>
@@ -19275,7 +19275,7 @@
         <v>142</v>
       </c>
       <c r="C45" s="45">
-        <v>11.05</v>
+        <v>19.880054999999999</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>98</v>
@@ -19289,7 +19289,7 @@
         <v>68</v>
       </c>
       <c r="C46" s="45">
-        <v>11.21</v>
+        <v>20.167911</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>98</v>
@@ -19303,7 +19303,7 @@
         <v>70</v>
       </c>
       <c r="C47" s="45">
-        <v>18.72</v>
+        <v>33.679151999999995</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>98</v>
@@ -19317,7 +19317,7 @@
         <v>73</v>
       </c>
       <c r="C48" s="45">
-        <v>9.6199999999999992</v>
+        <v>17.307341999999998</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>98</v>
@@ -19331,7 +19331,7 @@
         <v>75</v>
       </c>
       <c r="C49" s="45">
-        <v>72.239999999999995</v>
+        <v>129.966984</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>98</v>
@@ -19345,7 +19345,7 @@
         <v>32</v>
       </c>
       <c r="C50" s="45">
-        <v>4.58</v>
+        <v>8.2398779999999991</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>98</v>
@@ -19359,7 +19359,7 @@
         <v>137</v>
       </c>
       <c r="C51" s="45">
-        <v>4.78</v>
+        <v>8.5996980000000001</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>98</v>
@@ -19373,7 +19373,7 @@
         <v>70</v>
       </c>
       <c r="C52" s="45">
-        <v>46.51</v>
+        <v>83.676140999999987</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>98</v>
@@ -19387,7 +19387,7 @@
         <v>70</v>
       </c>
       <c r="C53" s="45">
-        <v>25.46</v>
+        <v>45.805086000000003</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>98</v>
@@ -19401,7 +19401,7 @@
         <v>137</v>
       </c>
       <c r="C54" s="45">
-        <v>27.79</v>
+        <v>49.996988999999999</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>98</v>
@@ -19415,7 +19415,7 @@
         <v>70</v>
       </c>
       <c r="C55" s="45">
-        <v>48.66</v>
+        <v>87.544205999999988</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>98</v>
@@ -19429,7 +19429,7 @@
         <v>81</v>
       </c>
       <c r="C56" s="45">
-        <v>12.98</v>
+        <v>23.352318</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>98</v>
@@ -19443,7 +19443,7 @@
         <v>147</v>
       </c>
       <c r="C57" s="45">
-        <v>5.08</v>
+        <v>9.1394280000000006</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>98</v>
@@ -19457,7 +19457,7 @@
         <v>83</v>
       </c>
       <c r="C58" s="45">
-        <v>7.69</v>
+        <v>13.835079</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>98</v>
@@ -19471,7 +19471,7 @@
         <v>142</v>
       </c>
       <c r="C59" s="45">
-        <v>37.409999999999997</v>
+        <v>67.304330999999991</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>98</v>
@@ -19485,7 +19485,7 @@
         <v>137</v>
       </c>
       <c r="C60" s="45">
-        <v>11.21</v>
+        <v>20.167911</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>98</v>
@@ -19499,7 +19499,7 @@
         <v>70</v>
       </c>
       <c r="C61" s="45">
-        <v>21.39</v>
+        <v>38.482748999999998</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>98</v>
@@ -19513,7 +19513,7 @@
         <v>68</v>
       </c>
       <c r="C62" s="45">
-        <v>14.83</v>
+        <v>26.680653</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>98</v>
@@ -19527,7 +19527,7 @@
         <v>151</v>
       </c>
       <c r="C63" s="45">
-        <v>3.47</v>
+        <v>6.242877</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>98</v>
@@ -19541,7 +19541,7 @@
         <v>70</v>
       </c>
       <c r="C64" s="45">
-        <v>7.47</v>
+        <v>13.439276999999999</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>98</v>
@@ -19555,7 +19555,7 @@
         <v>68</v>
       </c>
       <c r="C65" s="45">
-        <v>6.29</v>
+        <v>11.316338999999999</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>98</v>
@@ -19569,7 +19569,7 @@
         <v>86</v>
       </c>
       <c r="C66" s="45">
-        <v>6.19</v>
+        <v>11.136429</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>98</v>
@@ -19583,7 +19583,7 @@
         <v>142</v>
       </c>
       <c r="C67" s="45">
-        <v>12.52</v>
+        <v>22.524731999999997</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>98</v>
@@ -19597,7 +19597,7 @@
         <v>86</v>
       </c>
       <c r="C68" s="45">
-        <v>21.2</v>
+        <v>38.140919999999994</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>98</v>
@@ -19611,7 +19611,7 @@
         <v>36</v>
       </c>
       <c r="C69" s="45">
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>98</v>
@@ -19625,7 +19625,7 @@
         <v>34</v>
       </c>
       <c r="C70" s="45">
-        <v>12</v>
+        <v>21.589199999999998</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>98</v>
@@ -19639,7 +19639,7 @@
         <v>155</v>
       </c>
       <c r="C71" s="45">
-        <v>13.46</v>
+        <v>24.215886000000001</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>98</v>
@@ -19653,7 +19653,7 @@
         <v>49</v>
       </c>
       <c r="C72" s="45">
-        <v>13.22</v>
+        <v>23.784102000000001</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>98</v>
@@ -19667,7 +19667,7 @@
         <v>46</v>
       </c>
       <c r="C73" s="45">
-        <v>16.940000000000001</v>
+        <v>30.476754</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>98</v>
@@ -19681,7 +19681,7 @@
         <v>49</v>
       </c>
       <c r="C74" s="45">
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>98</v>
@@ -19695,7 +19695,7 @@
         <v>46</v>
       </c>
       <c r="C75" s="45">
-        <v>8.7200000000000006</v>
+        <v>15.688152000000001</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>98</v>
@@ -19709,7 +19709,7 @@
         <v>49</v>
       </c>
       <c r="C76" s="45">
-        <v>5.64</v>
+        <v>10.146923999999999</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>98</v>
@@ -19723,7 +19723,7 @@
         <v>46</v>
       </c>
       <c r="C77" s="45">
-        <v>17.850000000000001</v>
+        <v>32.113934999999998</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>98</v>
@@ -19737,7 +19737,7 @@
         <v>49</v>
       </c>
       <c r="C78" s="45">
-        <v>4.49</v>
+        <v>8.0779589999999999</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>98</v>
@@ -19751,7 +19751,7 @@
         <v>30</v>
       </c>
       <c r="C79" s="45">
-        <v>58.81</v>
+        <v>105.805071</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>98</v>
@@ -19765,7 +19765,7 @@
         <v>47</v>
       </c>
       <c r="C80" s="45">
-        <v>23.51</v>
+        <v>42.296841000000001</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>98</v>
@@ -19779,7 +19779,7 @@
         <v>93</v>
       </c>
       <c r="C81" s="45">
-        <v>22.65</v>
+        <v>40.749614999999999</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>98</v>
@@ -19793,7 +19793,7 @@
         <v>86</v>
       </c>
       <c r="C82" s="45">
-        <v>11.79</v>
+        <v>21.211388999999997</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>98</v>
@@ -19807,7 +19807,7 @@
         <v>81</v>
       </c>
       <c r="C83" s="45">
-        <v>7.51</v>
+        <v>13.511240999999998</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>98</v>
@@ -19821,7 +19821,7 @@
         <v>81</v>
       </c>
       <c r="C84" s="45">
-        <v>22.53</v>
+        <v>40.533723000000002</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>98</v>
@@ -19835,7 +19835,7 @@
         <v>96</v>
       </c>
       <c r="C85" s="45">
-        <v>28.61</v>
+        <v>51.472251</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>98</v>
@@ -19849,7 +19849,7 @@
         <v>86</v>
       </c>
       <c r="C86" s="45">
-        <v>5</v>
+        <v>8.9954999999999998</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>98</v>
@@ -19863,7 +19863,7 @@
         <v>65</v>
       </c>
       <c r="C87" s="45">
-        <v>0.98</v>
+        <v>1.763118</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>98</v>
@@ -20124,6 +20124,7 @@
   </sheetData>
   <autoFilter ref="A1:D105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -20329,20 +20330,20 @@
       </c>
     </row>
     <row r="19" spans="12:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M19" s="56" t="s">
+      <c r="M19" s="57" t="s">
         <v>226</v>
       </c>
-      <c r="N19" s="57"/>
-      <c r="O19" s="58"/>
-      <c r="P19" s="56" t="s">
+      <c r="N19" s="58"/>
+      <c r="O19" s="59"/>
+      <c r="P19" s="57" t="s">
         <v>227</v>
       </c>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="56" t="s">
+      <c r="Q19" s="58"/>
+      <c r="R19" s="59"/>
+      <c r="S19" s="57" t="s">
         <v>228</v>
       </c>
-      <c r="T19" s="58"/>
+      <c r="T19" s="59"/>
     </row>
     <row r="20" spans="12:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L20" t="s">
